--- a/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_20.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_20.xlsx
@@ -575,46 +575,46 @@
         <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>14.17322834645452</v>
+        <v>14.1279594605456</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12.56471320754435</v>
+        <v>12.52495304488892</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.64843952554269</v>
+        <v>-11.61137819660996</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.775177066362311</v>
+        <v>2.766738200136544</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-21.59608390745451</v>
+        <v>-21.52663622215881</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.76810986361236</v>
+        <v>-11.73003042939818</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.086999714716626</v>
+        <v>-7.063801578775923</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.983563778152956</v>
+        <v>1.977564211537995</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.922951263826278</v>
+        <v>1.917072163775515</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.071454069355603</v>
+        <v>1.06820999405727</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.640078335233873</v>
+        <v>5.622243990691942</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.675932696464464</v>
+        <v>5.657980960468201</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>5.255787313182722</v>
+        <v>5.239213225217</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.046511919171458</v>
+        <v>-4.033600036472215</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.493438320208845</v>
+        <v>-2.485576241234071</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8951943421795505</v>
+        <v>0.8925127625690976</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>20.5103067594556</v>
+        <v>20.44408866448214</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.132615777801973</v>
+        <v>3.122894876284199</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>17.60921110009548</v>
+        <v>17.55311667752011</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.898950433583451</v>
+        <v>7.874101666512871</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.816000576070316</v>
+        <v>7.791428240702295</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>12.35879498132504</v>
+        <v>12.31920277208501</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>24.82565853989045</v>
+        <v>24.74573725908827</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13.957437176813</v>
+        <v>13.91253496217375</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>13.75568227292065</v>
+        <v>13.71137233319105</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.28673099214839</v>
+        <v>11.25038992835189</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.360511234476697</v>
+        <v>8.333660834951168</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.613218479393254</v>
+        <v>8.585447582576535</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.493438320209975</v>
+        <v>-6.472319805844677</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-10.10756828303084</v>
+        <v>-10.07433573488498</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.504057391039282</v>
+        <v>-8.476908507791563</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.631533949372233</v>
+        <v>1.626500971050582</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.097014066865938</v>
+        <v>5.080560002286752</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.39853747705687</v>
+        <v>7.374762396958005</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13.32457002115914</v>
+        <v>13.28143055476355</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>16.86721491062035</v>
+        <v>16.81198568983182</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>14.80661277613067</v>
+        <v>14.75764086144168</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.949067565865263</v>
+        <v>9.916254789261913</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.736284292892329</v>
+        <v>5.717191727199818</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.783267565108787</v>
+        <v>9.751019642359921</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.364101206369476</v>
+        <v>9.333361670626353</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.590886756132022</v>
+        <v>1.585447582574481</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>58</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.217576251244459</v>
+        <v>-4.203426957744107</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-12.72899747750498</v>
+        <v>-12.68615091845292</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-7.952166664973525</v>
+        <v>-7.92610060460656</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-11.27486814969986</v>
+        <v>-11.23721616997256</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-8.364865863221482</v>
+        <v>-8.337106706739391</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.890202621577515</v>
+        <v>-2.880494824538033</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.248923035060798</v>
+        <v>-1.244896511829737</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.716892320472425</v>
+        <v>-1.711981511103019</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.05047878648530713</v>
+        <v>-0.05150449813164926</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.553394875926919</v>
+        <v>2.544216597815108</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.348732660491976</v>
+        <v>2.340353768644853</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.074048993531306</v>
+        <v>-1.071161046038149</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.225399735043609</v>
+        <v>-3.21521440034762</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.975839938277325</v>
+        <v>-2.966276555354852</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>89</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.057123477542582</v>
+        <v>7.033536769390508</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.199096288305903</v>
+        <v>3.189509633783778</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.81596871138062</v>
+        <v>-2.806340066141118</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.562051302274803</v>
+        <v>-1.555930212597112</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.52246659179557</v>
+        <v>3.510932270631159</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.946311008588459</v>
+        <v>4.929785420665134</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.862868663506241</v>
+        <v>4.846299367159105</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.396468259925328</v>
+        <v>4.380811871968163</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.588755937219759</v>
+        <v>6.565149700365779</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>10.24315865768369</v>
+        <v>10.20752017167345</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.660900627573561</v>
+        <v>6.63755963578506</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.570284132605238</v>
+        <v>5.550724495255494</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.277092365871937</v>
+        <v>6.2554064148256</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.27428957468188</v>
+        <v>4.259604885945677</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>110</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2338344070629574</v>
+        <v>0.2328368365806952</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>10.44316736120705</v>
+        <v>10.40774562515875</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.96051292237971</v>
+        <v>10.92250022294709</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>15.64276293003019</v>
+        <v>15.5890710355255</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>13.28801179585838</v>
+        <v>13.241724202963</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>14.49984262579994</v>
+        <v>14.44903779533188</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>14.41904248774164</v>
+        <v>14.36818237405443</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>12.13364795917608</v>
+        <v>12.090108011849</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>12.98736277570911</v>
+        <v>12.94012665715739</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>12.13874956517249</v>
+        <v>12.09457794108407</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>13.75960070446254</v>
+        <v>13.71019680372936</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>12.8859642174146</v>
+        <v>12.83978554028768</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>9.731598110877179</v>
+        <v>9.696676322523395</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>14.54591405734044</v>
+        <v>14.49453849166672</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>88</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.044454655149785</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9.533974636517812</v>
+        <v>9.499876503245929</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.867668341562499</v>
+        <v>6.842236326531527</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>11.54914727332454</v>
+        <v>11.50718383060319</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>14.42640615654706</v>
+        <v>14.37351870959471</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>13.59056515540097</v>
+        <v>13.54024538433349</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11.23324000877522</v>
+        <v>11.1910125389097</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>7.352982755245698</v>
+        <v>7.324184680152584</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.155714240669383</v>
+        <v>6.130361537012853</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.722859399355428</v>
+        <v>8.688508923872035</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>8.519970028235804</v>
+        <v>8.486631461142537</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>13.11606476361551</v>
+        <v>13.06654411866369</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>12.69770398925483</v>
+        <v>12.6502584084169</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>11.81165344077787</v>
+        <v>11.76726576439306</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>134</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6.461785560387042</v>
+        <v>6.437350764694237</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.865733960069058</v>
+        <v>1.857977646416359</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.711430474725148</v>
+        <v>3.696117185725726</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.34919659879565</v>
+        <v>2.3387697515805</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.177247360785373</v>
+        <v>-1.175486113856891</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.857315807707877</v>
+        <v>2.84370214254325</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.511314534841198</v>
+        <v>6.483959965418741</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.802083152964777</v>
+        <v>3.784657260358863</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>6.734691336204513</v>
+        <v>6.705576836020519</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.632830014106652</v>
+        <v>6.604068493856651</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7.17786873612291</v>
+        <v>7.147402961395549</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>10.20931011081292</v>
+        <v>10.16745152685824</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>10.53907420577956</v>
+        <v>10.49664128385978</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>14.53831178560667</v>
+        <v>14.4809699706351</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>148</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8849400581684037</v>
+        <v>0.8800957011563426</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.300871685367142</v>
+        <v>1.294654914599299</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.286801017978505</v>
+        <v>4.267964837202626</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.066055887875471</v>
+        <v>3.051968383248301</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.557672893616228</v>
+        <v>4.537320885342147</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.504143947566845</v>
+        <v>3.486873125222814</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.774695947345514</v>
+        <v>4.751779136376697</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>10.40198487316865</v>
+        <v>10.35747244008008</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.958598509254031</v>
+        <v>6.926163291751408</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>8.818678557016895</v>
+        <v>8.77901026466516</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.6161658304176</v>
+        <v>8.577551590267376</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>10.68784574847172</v>
+        <v>10.64060493580241</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>8.234801573929936</v>
+        <v>8.197740243599931</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>9.167309442824788</v>
+        <v>9.125988123115775</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>170</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.484951940075092</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.694607141570039</v>
+        <v>-4.676928255953669</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.736405505385562</v>
+        <v>-2.728405643595721</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.195489734477732</v>
+        <v>-3.185380867095205</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.557171281467333</v>
+        <v>-2.550464140434919</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.259423576456996</v>
+        <v>-2.254852858597474</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.112243270714764</v>
+        <v>-4.101110800794203</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.401847560696744</v>
+        <v>-3.394364124669792</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.5144907972580484</v>
+        <v>-0.51961058166264</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.7764861995366417</v>
+        <v>-0.7808847136976809</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.37856413644419</v>
+        <v>1.365684244722893</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.9461861050031359</v>
+        <v>-0.950577016550568</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.321095640947206</v>
+        <v>-4.310518984253832</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.07028948285717</v>
+        <v>-4.061611240953745</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>192</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.9309383202099752</v>
+        <v>-0.9282237614314468</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-7.753394024391902</v>
+        <v>-7.72026017189571</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.544807627558356</v>
+        <v>-5.523615540272871</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-11.15106657528045</v>
+        <v>-11.10510839121779</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.52117671216628</v>
+        <v>-7.492052411558106</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-9.3118830595823</v>
+        <v>-9.276064744419372</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-9.921102871189781</v>
+        <v>-9.883339959716984</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-11.43586942813439</v>
+        <v>-11.3925134483787</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-12.54387595708851</v>
+        <v>-12.49726201363134</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-11.3103071340944</v>
+        <v>-11.26939349223841</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-9.951057065465136</v>
+        <v>-9.916189198625631</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-8.873212407125308</v>
+        <v>-8.843635514203996</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-9.822320691243512</v>
+        <v>-9.786519837905637</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-6.957682214651015</v>
+        <v>-6.935385750758059</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>222</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.560615733844081</v>
+        <v>1.552022381096883</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.300737642340522</v>
+        <v>1.296263430918373</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.699769429088924</v>
+        <v>-2.68878058680999</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.291506493470408</v>
+        <v>3.276442340573901</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.9497585601785161</v>
+        <v>0.9434164238648322</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.151039605111784</v>
+        <v>2.138326559636887</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.261672227101684</v>
+        <v>0.257213716900786</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6575735954493567</v>
+        <v>-0.6584015108858168</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.621298336929136</v>
+        <v>-1.619058837041777</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2376798486368941</v>
+        <v>0.2304251060271199</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.937346934563152</v>
+        <v>0.9262423040687082</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.192159654878225</v>
+        <v>-2.18956607194275</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.09753982406115114</v>
+        <v>0.09206160563872601</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.364537995873974</v>
+        <v>-2.360498363370546</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>276</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.21807600136939</v>
+        <v>-3.203429698475823</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.867446812406705</v>
+        <v>3.848671525653401</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.0236250608951</v>
+        <v>2.012142354393248</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.243181789992228</v>
+        <v>3.225355995071929</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.254202699675467</v>
+        <v>1.245001520493837</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6248078160491062</v>
+        <v>-0.6255662934931365</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3798777073187978</v>
+        <v>0.3739097518295935</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4512637559514801</v>
+        <v>-0.4533348733968481</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1479784542647309</v>
+        <v>-0.1529859963744116</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4549030386709418</v>
+        <v>0.4450622119754541</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.433512101893619</v>
+        <v>2.412371210586954</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.6499657903867089</v>
+        <v>0.6382339307805935</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.682770907617034</v>
+        <v>1.6679169733004</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1152909290555684</v>
+        <v>0.1071867130101793</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>257</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.759479967727863</v>
+        <v>2.742808283096309</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7979200158113713</v>
+        <v>-0.7940059921132132</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.193181661025321</v>
+        <v>-1.188670548163472</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6732975573784756</v>
+        <v>-0.6725691037222035</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.0430531195195627</v>
+        <v>-0.0468958322375812</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.644246729545394</v>
+        <v>-3.627599993101548</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.731939736119358</v>
+        <v>1.716671723887195</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.296844852198241</v>
+        <v>-0.3003099442615991</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.918659879313203</v>
+        <v>-1.914550110230707</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.380142762720041</v>
+        <v>-2.375821208237603</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.7110892263373</v>
+        <v>-5.689841353217354</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.506159881110875</v>
+        <v>-4.490662102473458</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.149461379565913</v>
+        <v>-4.133893327886632</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.89870907329145</v>
+        <v>-3.885369538047257</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.192323078574368</v>
+        <v>-1.193724935604081</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.29304779728848</v>
+        <v>-4.300878897088893</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.945944455042181</v>
+        <v>-3.952616815009584</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.189340524483157</v>
+        <v>-4.196084924857558</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.377670557158631</v>
+        <v>-1.378775497657237</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.571382614903058</v>
+        <v>-2.575283569546428</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.163657506247581</v>
+        <v>-1.163606510860703</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4335663602375632</v>
+        <v>0.4361379920716217</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.781788424530419</v>
+        <v>-2.784832648182956</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.138780309507744</v>
+        <v>-2.139861566314892</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.209789146458945</v>
+        <v>-4.214524969548634</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.043817556002494</v>
+        <v>-6.052129043179001</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.475313799738402</v>
+        <v>-3.479569343539389</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-4.349084255531821</v>
+        <v>-4.35462732379164</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>264</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.1146504414221</v>
+        <v>-2.103085449239394</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6966448364825197</v>
+        <v>-0.6886829000915569</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.229973943907247</v>
+        <v>-2.214460771157519</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2032616683749922</v>
+        <v>-0.2021586328211242</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3975578592387379</v>
+        <v>0.3904730935178833</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8246625619054271</v>
+        <v>-0.820406518323523</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2339485388631175</v>
+        <v>0.2246964087730063</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.036348845639722</v>
+        <v>-4.01766977968505</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.577914075052853</v>
+        <v>-2.567087435397319</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.810554972134547</v>
+        <v>-3.795416971583442</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.160256749104235</v>
+        <v>-5.135206876225389</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.129948086589401</v>
+        <v>-5.102701594792862</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.174559892485831</v>
+        <v>-5.146578468755756</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-7.594042316316298</v>
+        <v>-7.550916053788107</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2667176724366911</v>
+        <v>-0.2681679742163539</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.905771468205401</v>
+        <v>-3.936874213665931</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.371712487057714</v>
+        <v>1.377310279728363</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.9302406811027595</v>
+        <v>-0.9364466302634327</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.686340718902336</v>
+        <v>-2.698564175631255</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.64195640460116</v>
+        <v>-5.679419694111289</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.099135695227396</v>
+        <v>-4.117152559934098</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.318915222192473</v>
+        <v>-1.323052858325845</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1607906601788471</v>
+        <v>-0.1575321709043038</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.650160010778059</v>
+        <v>1.668695954816911</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.04518956954605358</v>
+        <v>0.05012830493652132</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.317470468037001</v>
+        <v>-1.324522591740667</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.327901862020873</v>
+        <v>-1.335605411250462</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.956755013219535</v>
+        <v>0.9624967629032639</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.296261250605518</v>
+        <v>0.2958091112746573</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4005141944908317</v>
+        <v>0.4021331424090562</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8538637090344352</v>
+        <v>-0.8520419064867824</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.584197655009135</v>
+        <v>-1.581670177870663</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.123488671283226</v>
+        <v>-2.121206901688858</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3227152717098605</v>
+        <v>0.3235322610918629</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.540145782743586</v>
+        <v>1.536502211353742</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.362779897468748</v>
+        <v>2.358466273952246</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5768921919116821</v>
+        <v>0.5749906691446256</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.998462888137617</v>
+        <v>-1.997851063627564</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4827753764863232</v>
+        <v>-0.483259447867141</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4108019719037586</v>
+        <v>0.4100736921602461</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1988912090694512</v>
+        <v>-0.1985811715938013</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.380560897530323</v>
+        <v>-0.3800696588039614</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.928220928905624</v>
+        <v>-2.938703667028967</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.982205447146562</v>
+        <v>1.983152775680097</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.33165820664594</v>
+        <v>3.341557690928944</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.773824905562229</v>
+        <v>4.789583089387918</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.240579883809836</v>
+        <v>4.257097960351096</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.848736112039326</v>
+        <v>5.866574636908531</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.7647413352174937</v>
+        <v>0.7728332301469507</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.171013857722379</v>
+        <v>1.179588594183457</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.857805511697819</v>
+        <v>2.871889933034019</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.133462000809793</v>
+        <v>1.143125445710794</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3828533983205844</v>
+        <v>-0.3810331518889498</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.9620361967354896</v>
+        <v>0.9662468394623644</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1043205438265815</v>
+        <v>0.1045030976111647</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.348830018379935</v>
+        <v>2.357377407136752</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>196</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.567786169585915</v>
+        <v>0.5679292885323761</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.507034750301045</v>
+        <v>1.508025822720711</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9308216849895246</v>
+        <v>-0.9248976433713878</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.87212121525328</v>
+        <v>-3.850958232382254</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.413529592856626</v>
+        <v>-4.393923402539322</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.008876058759803</v>
+        <v>1.001638113439355</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.658985381558985</v>
+        <v>-2.654524175261443</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.05003412318439615</v>
+        <v>-0.06048308424708893</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4030522429378962</v>
+        <v>0.3887211112033029</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.9643833700373889</v>
+        <v>-0.9716081554572469</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.177519551026165</v>
+        <v>-1.176361479774826</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6329191521474655</v>
+        <v>-0.6317742407967444</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.05897727924944</v>
+        <v>-1.05202885174176</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.8040972659446339</v>
+        <v>-0.8023075194653586</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>178</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.371730219115811</v>
+        <v>5.332903917311604</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>9.390634240527056</v>
+        <v>9.328133709099227</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.248220089359066</v>
+        <v>2.231900850803939</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.946585566033555</v>
+        <v>2.925181754900208</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1526060527254884</v>
+        <v>0.1470123031253792</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1137119361168644</v>
+        <v>-0.1162247620479206</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.7544463752130426</v>
+        <v>-0.7627562321291919</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.92187792432091</v>
+        <v>-2.915332889337648</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4.113602729227871</v>
+        <v>-4.099928281137899</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.572593351141528</v>
+        <v>-1.579266949311965</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.622882447347827</v>
+        <v>-4.593009037674449</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.204171766824402</v>
+        <v>2.182947153378841</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4910551913476553</v>
+        <v>-0.4844984688020091</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.599000947518128</v>
+        <v>2.574211627519219</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.942713682528755</v>
+        <v>-3.999330877388452</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.6310972109507915</v>
+        <v>0.6517784684922034</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.082146454349335</v>
+        <v>2.125590697346574</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.150406593433402</v>
+        <v>1.179076950161203</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1058577967654841</v>
+        <v>-0.09458123667790375</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5361047775422634</v>
+        <v>-0.5365327104457123</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-8.651412077738364</v>
+        <v>-8.769414575866229</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-10.56241886249725</v>
+        <v>-10.71807945612913</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.168041174308819</v>
+        <v>-9.297597860829988</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-12.19834417379455</v>
+        <v>-12.36994526808014</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-10.16803728878627</v>
+        <v>-10.35247637017549</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-8.70138493385668</v>
+        <v>-8.83661173134854</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-6.901022070967372</v>
+        <v>-7.034644120071263</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-7.416540638154608</v>
+        <v>-7.525663528535674</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.961107134335457</v>
+        <v>2.979314221252913</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.286830114992412</v>
+        <v>-2.296025489757071</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>0.05255308493253352</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.084917947382131</v>
+        <v>1.097737597686496</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.310056701752288</v>
+        <v>8.369332575007526</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.987134214774194</v>
+        <v>5.022420738415903</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.170363997907188</v>
+        <v>2.185393443162042</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.534393504713051</v>
+        <v>3.553072429701565</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.647556297956562</v>
+        <v>1.657210158198218</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.44910575407701</v>
+        <v>4.476809743812538</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.999235165660295</v>
+        <v>7.024349997476563</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.373880304337568</v>
+        <v>3.389008384179746</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.790214183993243</v>
+        <v>4.80361615855599</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.200659233162398</v>
+        <v>3.218475105511132</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-6.779152605924303</v>
+        <v>-6.866932771894234</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.10501193317419</v>
+        <v>-4.15832315222405</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.59963363578894</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.344658207122393</v>
+        <v>1.386009660628829</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.6223344365212071</v>
+        <v>-0.5779930416289005</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.853093449672244</v>
+        <v>1.91113234591495</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3593043069511026</v>
+        <v>0.3771232663238777</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.09226628933244996</v>
+        <v>-0.09006013245771527</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1532661755147515</v>
+        <v>-0.1510600186400168</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4251800680288298</v>
+        <v>0.4480901586509844</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.695836579776753</v>
+        <v>1.692612196652206</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.421086247660824</v>
+        <v>7.524096803272961</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>11.31777152742635</v>
+        <v>11.45166827928463</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.242746567743197</v>
+        <v>7.353563524604375</v>
       </c>
     </row>
     <row r="30">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.01773</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4074~4087</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4074</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.01451372285339403</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.01649</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4053~4066</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4053</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.05861293899993569</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.01526</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4013~4026</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4013</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.0344219267673509</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.01402</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3963~3976</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3963</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.04680312848217483</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.01278</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3905~3918</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3905</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.1099307456399501</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.01154</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3816~3829</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3816</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.05154748709427537</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.0103</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3706~3719</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3706</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.059988468099192</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.009057</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3618~3631</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3618</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.1111744810472075</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.007818</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3484~3497</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3484</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.3630408366526439</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.006578</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3336~3349</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3336</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.4181919780182781</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.005338</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3166~3179</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3166</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.3072162377941225</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.004099</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2974~2987</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2974</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.2671242927576856</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.002859</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2752~2765</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2752</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.4138723165933342</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.00162</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2476~2489</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2476</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.1029200397760661</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.0003799</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2219~2232</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2219</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.4325064205684015</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.0008597</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1952~1963</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1952</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.328384830653178</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.002099</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1688~1699</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1688</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.05082501826765196</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.003339</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1444~1452</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1444</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.01409947723476535</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.004579</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1212~1219</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1212</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.07342191331908765</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.005818</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>984~989</t>
-        </is>
+      <c r="B25" t="n">
+        <v>984</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.5904848344917397</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.007058</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>788~793</t>
-        </is>
+      <c r="B26" t="n">
+        <v>788</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.5960950971922898</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.008297</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>610~615</t>
-        </is>
+      <c r="B27" t="n">
+        <v>610</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.7861212470392402</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.009537</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>475~477</t>
-        </is>
+      <c r="B28" t="n">
+        <v>475</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.127106753165279</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.01078</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>366~367</t>
-        </is>
+      <c r="B29" t="n">
+        <v>366</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.7223211539974415</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.01202</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>297~297</t>
-        </is>
+      <c r="B30" t="n">
+        <v>297</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.7052148784432291</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.01326</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>242~242</t>
-        </is>
+      <c r="B31" t="n">
+        <v>242</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.4273226177306313</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.0145</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>192~192</t>
-        </is>
+      <c r="B32" t="n">
+        <v>192</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.673228346456689</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.01573</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>142~142</t>
-        </is>
+      <c r="B33" t="n">
+        <v>142</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>3.14036449669144</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.01697</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>110~110</t>
-        </is>
+      <c r="B34" t="n">
+        <v>110</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>3.870198043426385</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.01821</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>8.220847394075733</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.01773</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.1124859392575885</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.01649</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>105~105</t>
-        </is>
+      <c r="B7" t="n">
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2.744656917885266</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.01526</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>145~145</t>
-        </is>
+      <c r="B8" t="n">
+        <v>145</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.299665128065882</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.01402</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>195~195</t>
-        </is>
+      <c r="B9" t="n">
+        <v>195</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.6985665253381725</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.01278</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>253~253</t>
-        </is>
+      <c r="B10" t="n">
+        <v>253</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-1.505296027719851</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.01154</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>342~342</t>
-        </is>
+      <c r="B11" t="n">
+        <v>342</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.7229359487958789</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.0103</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>452~452</t>
-        </is>
+      <c r="B12" t="n">
+        <v>452</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.6039068125333955</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.009057</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>540~540</t>
-        </is>
+      <c r="B13" t="n">
+        <v>540</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.8398950131233605</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.007818</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>674~674</t>
-        </is>
+      <c r="B14" t="n">
+        <v>674</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1.957600255457677</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.006578</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>822~822</t>
-        </is>
+      <c r="B15" t="n">
+        <v>822</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.764469222369101</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.005338</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>992~992</t>
-        </is>
+      <c r="B16" t="n">
+        <v>992</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.03478748624164</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.004099</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1184~1184</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1184</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.7160211392494844</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.002859</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1406~1406</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1406</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.8493781805012546</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.00162</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1682~1682</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1682</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.1819481244987102</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.0003799</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1939~1939</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1939</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.5235807617910524</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.0008597</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2206~2208</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2206</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.3145326942827751</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.002099</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2470~2472</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2470</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.05510536911041441</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.003339</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2714~2719</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2714</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.02587024911698421</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.004579</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2946~2952</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2946</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.04721208629408835</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.005818</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3174~3182</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3174</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.1678569248611339</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.007058</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3370~3378</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3370</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.1251730745024489</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.008297</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3548~3556</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3548</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.1499812523434514</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.009537</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3683~3694</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3683</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.002913144248950061</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.01078</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3792~3804</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3792</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.0827972213252437</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.01202</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3861~3874</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3861</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.04119257937362875</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.01326</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3916~3929</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3916</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.03901268513489242</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.0145</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3966~3979</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3966</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.06820584974001065</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.01573</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4016~4029</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4016</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.098303050912385</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.01697</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4048~4061</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4048</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.09255183904769382</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.01821</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4074~4087</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4074</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.1567610508192203</v>

--- a/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_20.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_20.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY MA Ratio-20 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY MA Ratio-20 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,150 +575,150 @@
         <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>14.1279594605456</v>
+        <v>14.14045182436563</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12.52495304488892</v>
+        <v>12.53783271752867</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.61137819660996</v>
+        <v>-11.59841483563831</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.766738200136544</v>
+        <v>2.779686108111434</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-21.52663622215881</v>
+        <v>-21.51356710046309</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.73003042939818</v>
+        <v>-11.7170197124729</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.063801578775923</v>
+        <v>-7.050761567914755</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.977564211537995</v>
+        <v>1.990725888347505</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.917072163775515</v>
+        <v>1.930254761358292</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.06820999405727</v>
+        <v>1.08160180353093</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.622243990691942</v>
+        <v>5.635692082650145</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.657980960468201</v>
+        <v>5.671427120218276</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>5.239213225217</v>
+        <v>5.252766153288057</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.033600036472215</v>
+        <v>-4.044029672172535</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01588</t>
+          <t>X ≈ -0.01587</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.485576241234071</v>
+        <v>-2.473097524407095</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8925127625690976</v>
+        <v>0.9053834772504885</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>20.44408866448214</v>
+        <v>20.45707307396859</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.122894876284199</v>
+        <v>3.135842555853728</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>17.55311667752011</v>
+        <v>17.56620677140466</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.874101666512871</v>
+        <v>7.887121523693231</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.791428240702295</v>
+        <v>7.804474250498821</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>12.31920277208501</v>
+        <v>12.33236801233146</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>24.74573725908827</v>
+        <v>24.75892669746608</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13.91253496217375</v>
+        <v>13.92592975957089</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>13.71137233319105</v>
+        <v>13.7248218063928</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.25038992835189</v>
+        <v>11.26383669947574</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.333660834951168</v>
+        <v>8.347213912522207</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.585447582576535</v>
+        <v>8.575017946877246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01464</t>
+          <t>X ≈ -0.01463</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.472319805844677</v>
+        <v>-6.459845408353793</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-10.07433573488498</v>
+        <v>-10.06147424304987</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.476908507791563</v>
+        <v>-8.463944487688842</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.626500971050582</v>
+        <v>1.639447030652939</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.080560002286752</v>
+        <v>5.093642719562631</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.374762396958005</v>
+        <v>7.387781565755233</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13.28143055476355</v>
+        <v>13.29447862340642</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>16.81198568983182</v>
+        <v>16.82515239049894</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>14.75764086144168</v>
+        <v>14.77082708977477</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.916254789261913</v>
+        <v>9.92964841489723</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.717191727199818</v>
+        <v>5.730639556026958</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.751019642359921</v>
+        <v>9.764466129492455</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.333361670626353</v>
+        <v>9.346914756263473</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.585447582574481</v>
+        <v>1.575017946877239</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>58</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.203426957744107</v>
+        <v>-4.190952101750099</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-12.68615091845292</v>
+        <v>-12.67329302355342</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-7.92610060460656</v>
+        <v>-7.913137539260234</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-11.23721616997256</v>
+        <v>-11.22427940749158</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-8.337106706739391</v>
+        <v>-8.324032582710728</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.880494824538033</v>
+        <v>-2.867481574855084</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.244896511829737</v>
+        <v>-1.231855435552497</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.711981511103019</v>
+        <v>-1.698822300790837</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.05150449813164926</v>
+        <v>-0.03832333039419922</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.544216597815108</v>
+        <v>2.557608045863191</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.340353768644853</v>
+        <v>2.353800703483266</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.071161046038149</v>
+        <v>-1.057716102427825</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.21521440034762</v>
+        <v>-3.20166220230174</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.966276555354852</v>
+        <v>-2.976706191053793</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>89</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.033536769390508</v>
+        <v>7.04601965756315</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.189509633783778</v>
+        <v>3.202378175963077</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.806340066141118</v>
+        <v>-2.793375059607207</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.555930212597112</v>
+        <v>-1.542988740243423</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.510932270631159</v>
+        <v>3.524012095436326</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.929785420665134</v>
+        <v>4.942801751542035</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.846299367159105</v>
+        <v>4.859342375677336</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.380811871968163</v>
+        <v>4.393972727088695</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.565149700365779</v>
+        <v>6.57833246461071</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>10.20752017167345</v>
+        <v>10.22091322419658</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.63755963578506</v>
+        <v>6.651007075869749</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.550724495255494</v>
+        <v>5.564170060427713</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.2554064148256</v>
+        <v>6.268959106828916</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.259604885945677</v>
+        <v>4.249175250247525</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>110</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2328368365806952</v>
+        <v>0.2453115446366496</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>10.40774562515875</v>
+        <v>10.42061837157431</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.92250022294709</v>
+        <v>10.9354738171773</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>15.5890710355255</v>
+        <v>15.6020228693666</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>13.241724202963</v>
+        <v>13.25480884343548</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>14.44903779533188</v>
+        <v>14.46205838149879</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>14.36818237405443</v>
+        <v>14.38122910857601</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>12.090108011849</v>
+        <v>12.10327125281733</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>12.94012665715739</v>
+        <v>12.95331101338689</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>12.09457794108407</v>
+        <v>12.10797105359877</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>13.71019680372936</v>
+        <v>13.72364533644124</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>12.83978554028768</v>
+        <v>12.85323184885399</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>9.696676322523395</v>
+        <v>9.710229109086825</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>14.49453849166672</v>
+        <v>14.48410885596856</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>88</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.044454655149785</v>
+        <v>2.056928576542219</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9.499876503245929</v>
+        <v>9.512746892103998</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.842236326531527</v>
+        <v>6.855205158899864</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>11.50718383060319</v>
+        <v>11.52013168842382</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>14.37351870959471</v>
+        <v>14.38660318156591</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>13.54024538433349</v>
+        <v>13.55326467027898</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11.1910125389097</v>
+        <v>11.20405692559216</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>7.324184680152584</v>
+        <v>7.337345073653658</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.130361537012853</v>
+        <v>6.14354278494249</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.688508923872035</v>
+        <v>8.70190054566342</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>8.486631461142537</v>
+        <v>8.500078491352056</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>13.06654411866369</v>
+        <v>13.07999024221997</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>12.6502584084169</v>
+        <v>12.66381128280599</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>11.76726576439306</v>
+        <v>11.75683612869542</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>134</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6.437350764694237</v>
+        <v>6.449826440079306</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.857977646416359</v>
+        <v>1.870838579476157</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.696117185725726</v>
+        <v>3.709081136976316</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.3387697515805</v>
+        <v>2.351708681189955</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.175486113856891</v>
+        <v>-1.16241414317463</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.84370214254325</v>
+        <v>2.856713461162393</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.483959965418741</v>
+        <v>6.497000668511831</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.784657260358863</v>
+        <v>3.797814839364598</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>6.705576836020519</v>
+        <v>6.718757385909811</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.604068493856651</v>
+        <v>6.617458763404549</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7.147402961395549</v>
+        <v>7.160849148300308</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>10.16745152685824</v>
+        <v>10.18089691985994</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>10.49664128385978</v>
+        <v>10.51019384563736</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>14.4809699706351</v>
+        <v>14.47054033493695</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>148</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8800957011563426</v>
+        <v>0.892561604700596</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.294654914599299</v>
+        <v>1.307511307708559</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.267964837202626</v>
+        <v>4.280926041769014</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.051968383248301</v>
+        <v>3.064904766064927</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.537320885342147</v>
+        <v>4.550394158496893</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.486873125222814</v>
+        <v>3.499882454500792</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.751779136376697</v>
+        <v>4.764816970150243</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>10.35747244008008</v>
+        <v>10.3706317822134</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.926163291751408</v>
+        <v>6.939342689001926</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>8.77901026466516</v>
+        <v>8.792400284570135</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.577551590267376</v>
+        <v>8.590997402409712</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>10.64060493580241</v>
+        <v>10.65404999440467</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>8.197740243599931</v>
+        <v>8.211292387208218</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>9.125988123115775</v>
+        <v>9.115558487417779</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>170</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.484951940075092</v>
+        <v>-2.472495867200195</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.676928255953669</v>
+        <v>-4.664084144682768</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.728405643595721</v>
+        <v>-2.715456179796597</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.185380867095205</v>
+        <v>-3.172454622818535</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.550464140434919</v>
+        <v>-2.537400523509213</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.254852858597474</v>
+        <v>-2.2418511246767</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.101110800794203</v>
+        <v>-4.088081590824828</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.394364124669792</v>
+        <v>-3.381214517251351</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.51961058166264</v>
+        <v>-0.5064364355464051</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.7808847136976809</v>
+        <v>-0.7674996311949229</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.365684244722893</v>
+        <v>1.379127031681378</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.950577016550568</v>
+        <v>-0.9371347637131535</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.310518984253832</v>
+        <v>-4.296968389109466</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.061611240953745</v>
+        <v>-4.07204087665216</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>192</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.9282237614314468</v>
+        <v>-0.9157737791387746</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-7.72026017189571</v>
+        <v>-7.707428798793799</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.523615540272871</v>
+        <v>-5.510676805988318</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-11.10510839121779</v>
+        <v>-11.09219780038067</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.492052411558106</v>
+        <v>-7.478999720044179</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-9.276064744419372</v>
+        <v>-9.263074452023957</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-9.883339959716984</v>
+        <v>-9.870320055420279</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-11.3925134483787</v>
+        <v>-11.37937320829938</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-12.49726201363134</v>
+        <v>-12.4840975320099</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-11.26939349223841</v>
+        <v>-11.25601552572989</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-9.916189198625631</v>
+        <v>-9.902751875118682</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-8.843635514203996</v>
+        <v>-8.830196237115949</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-9.786519837905637</v>
+        <v>-9.772970557834952</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-6.935385750758059</v>
+        <v>-6.945815386456083</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>222</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.552022381096883</v>
+        <v>1.564465628991485</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.296263430918373</v>
+        <v>1.309095615028113</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.68878058680999</v>
+        <v>-2.675848973689746</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.276442340573901</v>
+        <v>3.289359648715561</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.9434164238648322</v>
+        <v>0.9564692945828739</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.138326559636887</v>
+        <v>2.151319781202574</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.257213716900786</v>
+        <v>0.2702349058748013</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6584015108858168</v>
+        <v>-0.645259997116284</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.619058837041777</v>
+        <v>-1.605893309533116</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2304251060271199</v>
+        <v>0.2438043697166563</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9262423040687082</v>
+        <v>0.9396804771306506</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.18956607194275</v>
+        <v>-2.176127243325119</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.09206160563872601</v>
+        <v>0.1056110215384862</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.360498363370546</v>
+        <v>-2.370927999068698</v>
       </c>
     </row>
     <row r="18">
@@ -1199,150 +1199,150 @@
         <v>276</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.203429698475823</v>
+        <v>-3.19101159213254</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.848671525653401</v>
+        <v>3.861493482165535</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.012142354393248</v>
+        <v>2.025066494151496</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.225355995071929</v>
+        <v>3.238261775622334</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.245001520493837</v>
+        <v>1.258043582031412</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6255662934931365</v>
+        <v>-0.6125859872885755</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3739097518295935</v>
+        <v>0.3869222331729816</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4533348733968481</v>
+        <v>-0.4402010499154656</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1529859963744116</v>
+        <v>-0.1398260095491821</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4450622119754541</v>
+        <v>0.4584366048323716</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.412371210586954</v>
+        <v>2.425806477994826</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.6382339307805935</v>
+        <v>0.6516709444656783</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.6679169733004</v>
+        <v>1.681465347732527</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1071867130101793</v>
+        <v>0.09675707731202721</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0009999</t>
+          <t>X ≈ -0.001</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>257</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.742808283096309</v>
+        <v>2.755215546748822</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7940059921132132</v>
+        <v>-0.7812143983526525</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.188670548163472</v>
+        <v>-1.175772301630722</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6725691037222035</v>
+        <v>-0.6596872578641495</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.0468958322375812</v>
+        <v>-0.03387187282676507</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.627599993101548</v>
+        <v>-3.614639467605542</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.716671723887195</v>
+        <v>1.729673584097441</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.3003099442615991</v>
+        <v>-0.2871871300643889</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.914550110230707</v>
+        <v>-1.901400982525637</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.375821208237603</v>
+        <v>-2.362456140606348</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.689841353217354</v>
+        <v>-5.676415767339833</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.490662102473458</v>
+        <v>-4.477230638189354</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.133893327886632</v>
+        <v>-4.120347848225052</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.885369538047257</v>
+        <v>-3.895799173745409</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002399</t>
+          <t>X ≈ 0.0002395</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>267</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.193724935604081</v>
+        <v>-1.181161748229286</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.300878897088893</v>
+        <v>-4.287923071371225</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.952616815009584</v>
+        <v>-3.939548533437922</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.196084924857558</v>
+        <v>-4.183031824956409</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.378775497657237</v>
+        <v>-1.365571266244324</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.575283569546428</v>
+        <v>-2.562136931602481</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.163606510860703</v>
+        <v>-1.150422067400122</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4361379920716217</v>
+        <v>0.2475768890256234</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.784832648182956</v>
+        <v>-2.974616227492902</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.139861566314892</v>
+        <v>-2.126507160348389</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.214524969548634</v>
+        <v>-4.201107391739491</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.052129043179001</v>
+        <v>-6.038704306213816</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.479569343539389</v>
+        <v>-3.466026690495163</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-4.35462732379164</v>
+        <v>-4.365056959489792</v>
       </c>
     </row>
     <row r="21">
@@ -1355,150 +1355,150 @@
         <v>264</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.103085449239394</v>
+        <v>-2.090741825321864</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6886829000915569</v>
+        <v>-0.6759411764685126</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.214460771157519</v>
+        <v>-2.201608795218824</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2021586328211242</v>
+        <v>-0.1893105874771663</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3904730935178833</v>
+        <v>0.4034723982384065</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.820406518323523</v>
+        <v>-0.8074633681922947</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2246964087730063</v>
+        <v>0.2376844965222773</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.01766977968505</v>
+        <v>-4.006186867294815</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.567087435397319</v>
+        <v>-2.554872936411208</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.795416971583442</v>
+        <v>-3.782081015001097</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.135206876225389</v>
+        <v>-5.121803464311043</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.102701594792862</v>
+        <v>-5.089285704493363</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.146578468755756</v>
+        <v>-5.133040828614014</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-7.550916053788107</v>
+        <v>-7.561345689486259</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.002719</t>
+          <t>X ≈ 0.002718</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>244</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2681679742163539</v>
+        <v>-0.2554391632673685</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.936874213665931</v>
+        <v>-3.923740676811946</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.377310279728363</v>
+        <v>1.390582660577209</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.9364466302634327</v>
+        <v>-0.9231876604927436</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.698564175631255</v>
+        <v>-2.685154145782718</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.679419694111289</v>
+        <v>-5.666056686187666</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.117152559934098</v>
+        <v>-4.103746201167034</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.323052858325845</v>
+        <v>-1.310301259167112</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1575321709043038</v>
+        <v>-0.1439952610038731</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.668695954816911</v>
+        <v>1.459292492296946</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.05012830493652132</v>
+        <v>-0.1633192626455227</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.324522591740667</v>
+        <v>-1.540942045201895</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.335605411250462</v>
+        <v>-1.322073031187855</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9624967629032639</v>
+        <v>0.9520671272050691</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.003959</t>
+          <t>X ≈ 0.003958</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>232</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2958091112746573</v>
+        <v>0.3082804215537323</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4021331424090562</v>
+        <v>0.4150142016789999</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8520419064867824</v>
+        <v>-0.8390319084319984</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.581670177870663</v>
+        <v>-1.568657779545781</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.121206901688858</v>
+        <v>-2.108030541348214</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3235322610918629</v>
+        <v>0.3366762315857059</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.536502211353742</v>
+        <v>1.549699507060566</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.358466273952246</v>
+        <v>2.374086783925527</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5749906691446256</v>
+        <v>0.5892647838390772</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.997851063627564</v>
+        <v>-1.984791943525266</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.483259447867141</v>
+        <v>-0.4695283953420457</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4100736921602461</v>
+        <v>0.4239378478226357</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1985811715938013</v>
+        <v>-0.4293341005448994</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3800696588039614</v>
+        <v>-0.3904992945021135</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.938703667028967</v>
+        <v>-2.910861559270039</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.983152775680097</v>
+        <v>1.994638627614854</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.341557690928944</v>
+        <v>3.340035684868958</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.789583089387918</v>
+        <v>4.779467650158708</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.257097960351096</v>
+        <v>4.246038510117756</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.866574636908531</v>
+        <v>5.853550227685922</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.7728332301469507</v>
+        <v>0.5438719507918108</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.179588594183457</v>
+        <v>1.182534837979226</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.871889933034019</v>
+        <v>2.868277572286132</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.143125445710794</v>
+        <v>1.144996330541439</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3810331518889498</v>
+        <v>-0.36974849584103</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.9662468394623644</v>
+        <v>0.9746733246365693</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1045030976111647</v>
+        <v>0.1178412486158322</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.357377407136752</v>
+        <v>2.526983012379432</v>
       </c>
     </row>
     <row r="25">
@@ -1563,98 +1563,98 @@
         <v>196</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5679292885323761</v>
+        <v>0.5800747958397778</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.508025822720711</v>
+        <v>1.520777051510017</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9248976433713878</v>
+        <v>-0.9109903272068891</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.850958232382254</v>
+        <v>-3.833969486612617</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.393923402539322</v>
+        <v>-4.377038920636203</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.001638113439355</v>
+        <v>1.013165165319137</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.654524175261443</v>
+        <v>-2.641457920960967</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.06048308424708893</v>
+        <v>-0.04730207495185113</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3887211112033029</v>
+        <v>0.4019198501580661</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.9716081554572469</v>
+        <v>-0.9582030278044158</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.176361479774826</v>
+        <v>-1.162904186064608</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6317742407967444</v>
+        <v>-0.6183219520766343</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.05202885174176</v>
+        <v>-1.038472805390157</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.8023075194653586</v>
+        <v>-0.8127371551635107</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.007678</t>
+          <t>X ≈ 0.007677</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>178</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.332903917311604</v>
+        <v>5.337085315471924</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>9.328133709099227</v>
+        <v>9.328072877562406</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.231900850803939</v>
+        <v>2.241215122344919</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.925181754900208</v>
+        <v>2.933562754623168</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1470123031253792</v>
+        <v>0.1587830917114559</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1162247620479206</v>
+        <v>-0.1037960128451019</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.7627562321291919</v>
+        <v>-0.7496899778287158</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.915332889337648</v>
+        <v>-2.90215188004241</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4.099928281137899</v>
+        <v>-4.086729542183136</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.579266949311965</v>
+        <v>-1.565861821659134</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.593009037674449</v>
+        <v>-4.579551743964231</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.182947153378841</v>
+        <v>2.196399442098951</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4844984688020091</v>
+        <v>-0.4709424224504062</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.574211627519219</v>
+        <v>2.563781991821067</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>135</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.999330877388452</v>
+        <v>-3.978759578587088</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.6517784684922034</v>
+        <v>0.2710036318479041</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.125590697346574</v>
+        <v>1.740027188258416</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.179076950161203</v>
+        <v>0.7945918080723757</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.09458123667790375</v>
+        <v>-0.08318326025560197</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5365327104457123</v>
+        <v>-0.5236248017707084</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-8.769414575866229</v>
+        <v>-8.756348321565753</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-10.71807945612913</v>
+        <v>-10.70489844683389</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.297597860829988</v>
+        <v>-9.284399121875225</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-12.36994526808014</v>
+        <v>-12.35654014042731</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-10.35247637017549</v>
+        <v>-10.33901907646528</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-8.83661173134854</v>
+        <v>-8.82315944262843</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-7.034644120071263</v>
+        <v>-7.02108807371966</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-7.525663528535674</v>
+        <v>-7.536093164233826</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>109</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.979314221252913</v>
+        <v>2.984492123704882</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.296025489757071</v>
+        <v>-2.28311568018102</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.05255308493253352</v>
+        <v>0.06556021635013565</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.097737597686496</v>
+        <v>1.11071674008496</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.369332575007526</v>
+        <v>7.889184509854623</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.022420738415903</v>
+        <v>5.020091888431622</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.185393443162042</v>
+        <v>2.198459697462518</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.553072429701565</v>
+        <v>3.566253438996803</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.657210158198218</v>
+        <v>1.670408897152981</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.476809743812538</v>
+        <v>4.490214871465369</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.024349997476563</v>
+        <v>7.03780729118678</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.389008384179746</v>
+        <v>3.402460672899856</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.80361615855599</v>
+        <v>4.817172204907592</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.218475105511132</v>
+        <v>3.20804546981298</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>69</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-6.866932771894234</v>
+        <v>-6.832231035418843</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.15832315222405</v>
+        <v>-4.145413342647998</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.59963363578894</v>
+        <v>5.612640767206543</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.386009660628829</v>
+        <v>1.398988803027294</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5779930416289005</v>
+        <v>-0.5648822372539613</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.91113234591495</v>
+        <v>1.165971237944419</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3771232663238777</v>
+        <v>0.3901895206243537</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.09006013245771527</v>
+        <v>-0.07687912316247747</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1510600186400168</v>
+        <v>-0.1378612796852536</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4480901586509844</v>
+        <v>0.4614952863038155</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.692612196652206</v>
+        <v>1.706069490362424</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.524096803272961</v>
+        <v>7.537549091993071</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>11.45166827928463</v>
+        <v>11.46522432563623</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.353563524604375</v>
+        <v>7.343133888906223</v>
       </c>
     </row>
     <row r="30">
@@ -1823,98 +1823,98 @@
         <v>55</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.68837986160824</v>
+        <v>4.736899710771283</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.894988066825718</v>
+        <v>5.907897876401769</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.318301178410991</v>
+        <v>7.331308309828593</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>11.08491794738213</v>
+        <v>11.0978970897806</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.72831491412812</v>
+        <v>8.741425718503059</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19.93484776093472</v>
+        <v>19.94789065722908</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16.2137504072988</v>
+        <v>16.22681666159927</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>17.56474882669917</v>
+        <v>17.5779298359944</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>17.50374894051686</v>
+        <v>17.51694767947163</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>14.83544193730701</v>
+        <v>14.84884706495984</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>18.26705224935317</v>
+        <v>18.28050954306339</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>14.665071770335</v>
+        <v>14.67852405905511</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>14.24481715939002</v>
+        <v>14.25837320574162</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>9.03999303712088</v>
+        <v>9.029563401422728</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.01388</t>
+          <t>X ≈ 0.01387</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>50</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-8.493438320209947</v>
+        <v>-8.480916030534324</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.105011933174232</v>
+        <v>-2.092102123598181</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-8.499880639770822</v>
+        <v>-8.48687350835322</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.630372492836685</v>
+        <v>1.643351635235149</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.091951277764537</v>
+        <v>1.105062082139476</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6106067845198311</v>
+        <v>-0.5975638882254657</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6953405017921099</v>
+        <v>-0.6822742474916339</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.278402296101476</v>
+        <v>-4.264945002391258</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-8.244019138756016</v>
+        <v>-8.230566850035906</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.664273749700889</v>
+        <v>-2.650717703349287</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-6.41455241742463</v>
+        <v>-6.424982053122783</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>50</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.493438320210004</v>
+        <v>-2.480916030534381</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.369627507163322</v>
+        <v>-6.356648364764858</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-8.90804872223552</v>
+        <v>-8.894937917860581</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.6106067845198524</v>
+        <v>-0.597563888225487</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.304659498207897</v>
+        <v>1.317725752508373</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.837476099426389</v>
+        <v>6.850657108721627</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.776476213244116</v>
+        <v>4.78967495219888</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.926351028216153</v>
+        <v>1.939756155868984</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.721597703898553</v>
+        <v>1.735054997608771</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2440191387559594</v>
+        <v>-0.2305668500358493</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.6642737497008611</v>
+        <v>-0.6507177033492582</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.414552417424581</v>
+        <v>-4.424982053122733</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>32</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.6315616797900674</v>
+        <v>0.6440839694656901</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.144988066825789</v>
+        <v>2.15789787640184</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.750119360229178</v>
+        <v>1.76312649164678</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.880372492836678</v>
+        <v>1.893351635235142</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-8.033048722235449</v>
+        <v>-8.01993791786051</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-10.86060678451981</v>
+        <v>-10.84756388822544</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.804659498207869</v>
+        <v>7.817725752508345</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10.46247609942642</v>
+        <v>10.47565710872166</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.276476213244045</v>
+        <v>7.289674952198808</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.42635102821616</v>
+        <v>6.439756155868992</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.47159770389862</v>
+        <v>12.48505499760884</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.13098086124397</v>
+        <v>3.14443314996408</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.835726250299068</v>
+        <v>5.849282296650671</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.210447582575355</v>
+        <v>9.200017946877203</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>26</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-10.18574601251764</v>
+        <v>-10.17322372284202</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-7.9511657793281</v>
+        <v>-7.938255969752049</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-27.5768037166939</v>
+        <v>-27.5637965852763</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-27.4465505840864</v>
+        <v>-27.43357144168793</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-24.13881795300472</v>
+        <v>-24.12570714862978</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-31.53368370759675</v>
+        <v>-31.52064081130239</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-39.31072511717669</v>
+        <v>-39.29765886287622</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-28.23944697749672</v>
+        <v>-28.22626596820148</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-20.6081391713713</v>
+        <v>-20.59494043241654</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-25.30441820255307</v>
+        <v>-25.29101307490024</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-21.66301768071681</v>
+        <v>-21.64956038700659</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-17.78248067721752</v>
+        <v>-17.76902838849741</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-22.04888913431628</v>
+        <v>-22.03533308796467</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-21.79916780204002</v>
+        <v>-21.80959743773817</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY MA Ratio-20 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY MA Ratio-20 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.01451372285339403</v>
+        <v>0.014191601559574</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1289577192976239</v>
+        <v>0.1285976561913884</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.05679618444646906</v>
+        <v>-0.05711335172082244</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1357593684488236</v>
+        <v>0.1353956988826326</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1250152013501094</v>
+        <v>0.1246507207290719</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1419654839760085</v>
+        <v>0.1415984923770353</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1686634188155836</v>
+        <v>0.1682892017979327</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1070839425636478</v>
+        <v>0.1067217987485805</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.08414966261894108</v>
+        <v>0.08379259925767713</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.05680713415043925</v>
+        <v>0.05645142431713879</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.06204411057015591</v>
+        <v>0.06168569893297615</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.0611820388691342</v>
+        <v>0.06082387844094228</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.07192256931751473</v>
+        <v>0.07155903855454682</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.008072299604279465</v>
+        <v>-0.007804139012328903</v>
       </c>
     </row>
     <row r="7">
@@ -2266,101 +2266,101 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.05861293899993569</v>
+        <v>-0.05898340206127273</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.06472976424274179</v>
+        <v>0.06431696149773813</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.00307211613468894</v>
+        <v>0.002671387095730893</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1221273537768681</v>
+        <v>0.1216980919280601</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2371999237517102</v>
+        <v>0.2367381835423501</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.2034784161696592</v>
+        <v>0.2030269537243186</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2061373307202032</v>
+        <v>0.2056843833874638</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.09739233495238864</v>
+        <v>0.09696252744083722</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.07465265484093209</v>
+        <v>0.07422779772731047</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.05156670482449499</v>
+        <v>0.05114107454814132</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.03323478476642805</v>
+        <v>0.03281196088215665</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.03218308072612786</v>
+        <v>0.03176056613769873</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.04514904260300767</v>
+        <v>0.04472002784676476</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.01278535706342865</v>
+        <v>0.01310378802179457</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01526</t>
+          <t>X &gt; -0.01525</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4013</v>
+        <v>4014</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0344219267673509</v>
+        <v>-0.03492646013455669</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.05647875005558234</v>
+        <v>0.05593563099695587</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2006758683990526</v>
+        <v>-0.2011592226389354</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.09221688756697688</v>
+        <v>0.09166177440015133</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.06460170043979474</v>
+        <v>0.06404791360849771</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.127020671336922</v>
+        <v>0.1264540133160565</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1305301449740597</v>
+        <v>0.1299615147565589</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02442984732653031</v>
+        <v>-0.02496478182563777</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1712589783935385</v>
+        <v>-0.1717582401375495</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.08659395560260919</v>
+        <v>-0.08712288843165794</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.103103491320546</v>
+        <v>-0.103630588649601</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.07963557711214975</v>
+        <v>-0.08016844366137832</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.03746757132520173</v>
+        <v>-0.03801533722226225</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.07266355622351028</v>
+        <v>-0.0722167317475666</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3963</v>
+        <v>3964</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.04680312848217483</v>
+        <v>0.04611439440906651</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1842962429263935</v>
+        <v>0.1835517999430607</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.0962570866757062</v>
+        <v>-0.09693640143498072</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.07285927864085551</v>
+        <v>0.07213875149080451</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.001316836676892308</v>
+        <v>0.0006070104052398051</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.03557805557083071</v>
+        <v>0.03486310069698817</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.03539087962585796</v>
+        <v>-0.03608940740097211</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2368499272805877</v>
+        <v>-0.2375041003463849</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.3596124964333356</v>
+        <v>-0.3602368643796297</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2127969425426031</v>
+        <v>-0.2134696505826241</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1765364362930413</v>
+        <v>-0.1772212816954664</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2036660492225764</v>
+        <v>-0.2043439554317388</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1556965549481149</v>
+        <v>-0.1563923565649148</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.09358345451771299</v>
+        <v>-0.09299416210357947</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3905</v>
+        <v>3906</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1099307456399501</v>
+        <v>0.1090303843674008</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3754578140813223</v>
+        <v>0.3744624501639393</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.02003764419240639</v>
+        <v>0.01912598105193553</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2408450343437067</v>
+        <v>0.2398787036723249</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1251653809837165</v>
+        <v>0.1242191702620516</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.07888976544183635</v>
+        <v>0.07795987263299509</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.01742639136266178</v>
+        <v>-0.01833353703928964</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2149401623992304</v>
+        <v>-0.2158050589675327</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.3641887483927491</v>
+        <v>-0.3650169424572454</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2537461833469052</v>
+        <v>-0.2546172456655356</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2139191845353992</v>
+        <v>-0.2148043014446657</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1907813604094315</v>
+        <v>-0.1916722748055832</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1102542924556289</v>
+        <v>-0.111173295875524</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.05091605378824227</v>
+        <v>-0.05017406541153946</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3816</v>
+        <v>3817</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.05154748709427537</v>
+        <v>-0.05271759711398261</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3098261023534619</v>
+        <v>0.3085246719097867</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.08595683083278516</v>
+        <v>0.0847043390866915</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2827509559835661</v>
+        <v>0.2814493619139995</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.04619964377757668</v>
+        <v>0.04494707952574828</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.0342469518838513</v>
+        <v>-0.03547238495749383</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1308623432778617</v>
+        <v>-0.1320650424707139</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.3221262030330578</v>
+        <v>-0.3232900531931051</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5258006776221791</v>
+        <v>-0.5269132215321832</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4977327414173445</v>
+        <v>-0.4988724753793718</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3737152052399395</v>
+        <v>-0.374892646370256</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3246896468754201</v>
+        <v>-0.3258797591743985</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2587196496223001</v>
+        <v>-0.2599371899915113</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1514496920577244</v>
+        <v>-0.1504208794261288</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3706</v>
+        <v>3707</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.059988468099192</v>
+        <v>-0.0615611918246799</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.01010372040295948</v>
+        <v>0.008462544323300847</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2356890874436743</v>
+        <v>-0.2372769510643593</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1715650744399611</v>
+        <v>-0.1731670626394859</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3454646037967279</v>
+        <v>-0.3470369490769158</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4641339789193992</v>
+        <v>-0.4656661762470051</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.5612171514015927</v>
+        <v>-0.5627265899795191</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.6905411419529273</v>
+        <v>-0.6920307447661216</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.9254909115201215</v>
+        <v>-0.9269198753873553</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.8714926375520307</v>
+        <v>-0.8729627878119572</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.7917482114424814</v>
+        <v>-0.7932468891836564</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7154322994895423</v>
+        <v>-0.7169513202434885</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.5542117049207462</v>
+        <v>-0.5557878220116379</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.5861660169928768</v>
+        <v>-0.5846799220194399</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3618</v>
+        <v>3619</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1111744810472075</v>
+        <v>-0.113074620842724</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2207144125130682</v>
+        <v>-0.2226446738598113</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4078442661141608</v>
+        <v>-0.4097385221273271</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4556253020916543</v>
+        <v>-0.4575025945802409</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7034719370135463</v>
+        <v>-0.7053017546852516</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.8047601215303075</v>
+        <v>-0.806552032697482</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.8470646397231505</v>
+        <v>-0.8488489854949393</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8854819579687572</v>
+        <v>-0.8872739257611286</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.097109213198088</v>
+        <v>-1.098846019103576</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.104018933131165</v>
+        <v>-1.105786212334159</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.017424665612602</v>
+        <v>-1.01922440603559</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.050648973010126</v>
+        <v>-1.052439260972079</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.8753817905961654</v>
+        <v>-0.8772370403658627</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.8866364417474344</v>
+        <v>-0.8847775767480641</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3484</v>
+        <v>3485</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3630408366526439</v>
+        <v>-0.3654214622095893</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.3006641070872789</v>
+        <v>-0.30314015619755</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.565688937338777</v>
+        <v>-0.5681092062937267</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5631020349252012</v>
+        <v>-0.5655181787848846</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6853175455964973</v>
+        <v>-0.6877255538078941</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.9450855932254427</v>
+        <v>-0.9474064304527801</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.129027124536307</v>
+        <v>-1.131300593425195</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.06510269713521</v>
+        <v>-1.067417941407278</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.397212522783427</v>
+        <v>-1.399436795652157</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.400483834169165</v>
+        <v>-1.402748859894842</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.331456497420604</v>
+        <v>-1.33375234184075</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.482114376851221</v>
+        <v>-1.484366677968197</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.312767293459864</v>
+        <v>-1.315089476154796</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.477698226839067</v>
+        <v>-1.475197261157192</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4181919780182781</v>
+        <v>-0.421214537997038</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3714396512148568</v>
+        <v>-0.3745745034130437</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7801316107896454</v>
+        <v>-0.7831698046495106</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7234828568345719</v>
+        <v>-0.7265318425061196</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.9170173321009685</v>
+        <v>-0.9200425203710125</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.141707262988731</v>
+        <v>-1.144649090019193</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.389926203257865</v>
+        <v>-1.392800563281099</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.571859627683125</v>
+        <v>-1.574709328610112</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.766474998967823</v>
+        <v>-1.769271786281102</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.852092085556301</v>
+        <v>-1.854916097947232</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.771064769895972</v>
+        <v>-1.77392703831935</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.019932859546884</v>
+        <v>-2.022720189359028</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.734696284912154</v>
+        <v>-1.73759607363089</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.948125558911407</v>
+        <v>-1.944910132235734</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3166</v>
+        <v>3167</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3072162377941225</v>
+        <v>-0.3111047097796273</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1402542239231366</v>
+        <v>-0.1443198021134435</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.6755180335385305</v>
+        <v>-0.6794474542311306</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5912899756771779</v>
+        <v>-0.5952382294170491</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.8293085647551806</v>
+        <v>-0.8332250715129419</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.08193633713482</v>
+        <v>-1.085752864603421</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.24434775045269</v>
+        <v>-1.248121758518728</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.473999310409674</v>
+        <v>-1.477738731177524</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.833426025797223</v>
+        <v>-1.83705896961704</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.909611116894247</v>
+        <v>-1.913287048167589</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.939494123176203</v>
+        <v>-1.943178440877006</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.077352472089323</v>
+        <v>-2.080992851929217</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.596386158920971</v>
+        <v>-1.600212652844235</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.834640857096119</v>
+        <v>-1.830728816621331</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2671242927576856</v>
+        <v>-0.2720806891688881</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3491072898666232</v>
+        <v>0.343786728092482</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3625272059349811</v>
+        <v>-0.3676504674958849</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.08747705047742471</v>
+        <v>0.08221260675942688</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3991650480819544</v>
+        <v>-0.4043212958766418</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5529273747277514</v>
+        <v>-0.55800639576821</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6866185963912415</v>
+        <v>-0.6916639188531377</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8336648401709184</v>
+        <v>-0.8387088758473169</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.144973937813312</v>
+        <v>-1.149922363237394</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.305348098714667</v>
+        <v>-1.310327764909793</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.424522551391973</v>
+        <v>-1.4294849620957</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.640524515100076</v>
+        <v>-1.645414011607926</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.067635094238703</v>
+        <v>-1.072760714101975</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.505339236523461</v>
+        <v>-1.500612305223591</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4138723165933342</v>
+        <v>-0.4201785034193861</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2727015255811978</v>
+        <v>0.2659448926766856</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1748715916347336</v>
+        <v>-0.1815189497425109</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.169772329755645</v>
+        <v>-0.1764094939722369</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5074692220544037</v>
+        <v>-0.5140545000473793</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7700270743749016</v>
+        <v>-0.7764845691381836</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7627562321291919</v>
+        <v>-0.7692307692307665</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.8478030883908758</v>
+        <v>-0.8543084585128753</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.106730170506367</v>
+        <v>-1.113153184131825</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.429236780201833</v>
+        <v>-1.435651896361691</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.614155472144979</v>
+        <v>-1.620532810809195</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.596234098814087</v>
+        <v>-1.602617666732797</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.161186208836376</v>
+        <v>-1.167783789042822</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.436354743006</v>
+        <v>-1.430430654648362</v>
       </c>
     </row>
     <row r="19">
@@ -2890,153 +2890,153 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1029200397760661</v>
+        <v>-0.1114381188877616</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1259122547176474</v>
+        <v>-0.1346895080899415</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4186582835183117</v>
+        <v>-0.4273879778065961</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5482276680643707</v>
+        <v>-0.556889619288377</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.7028173339055144</v>
+        <v>-0.7115107255838069</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.7861301339562274</v>
+        <v>-0.7947469868170174</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.8894605179016537</v>
+        <v>-0.8980552458813307</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.8917745049249461</v>
+        <v>-0.9004504224906142</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.213044141451604</v>
+        <v>-1.221606272619837</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.638165100816103</v>
+        <v>-1.646700917891586</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.062992856811377</v>
+        <v>-2.071396615294418</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.845310502759212</v>
+        <v>-1.853802025509864</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.476546660480061</v>
+        <v>-1.485261690435649</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.608413483660463</v>
+        <v>-1.600597717232567</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003799</t>
+          <t>X &gt; -0.0003802</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4325064205684015</v>
+        <v>-0.4432984756754124</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.04853501699314933</v>
+        <v>-0.05984405908205304</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3294770523268724</v>
+        <v>-0.3407506934720033</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.5338266996263101</v>
+        <v>-0.5449891719397471</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7787848084114373</v>
+        <v>-0.7899581062858587</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4570369596433181</v>
+        <v>-0.4682999744014111</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.191297375107482</v>
+        <v>-1.2022562861086</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.960276709562379</v>
+        <v>-0.9714453171543838</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.131797168050873</v>
+        <v>-1.142909317464074</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.552731292971423</v>
+        <v>-1.563840966433162</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.642938749746783</v>
+        <v>-1.654058812557636</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.538931340466931</v>
+        <v>-1.550098803231201</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.168778254205392</v>
+        <v>-1.180208923520375</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.344701133062273</v>
+        <v>-1.334891963032661</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0008597</t>
+          <t>X &gt; 0.0008593</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.328384830653178</v>
+        <v>-0.3424231588439284</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.5331124297207666</v>
+        <v>0.5181882482815965</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1661061016876175</v>
+        <v>0.1512508545417788</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.03289281328576976</v>
+        <v>-0.0476223576256416</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6967164098311969</v>
+        <v>-0.7112644484728037</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1672972850305499</v>
+        <v>-0.1820457667349089</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.19508500869042</v>
+        <v>-1.209342684672428</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.15128220409941</v>
+        <v>-1.138101194804172</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9056903682582131</v>
+        <v>-0.8924916293034499</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.472421977918813</v>
+        <v>-1.486917323947054</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.291190019886585</v>
+        <v>-1.30584479789222</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9216035809258898</v>
+        <v>-0.9364492029770517</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.8527018090966934</v>
+        <v>-0.8677084914762077</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9329950403754168</v>
+        <v>-0.9206297745769234</v>
       </c>
     </row>
     <row r="22">
@@ -3046,153 +3046,153 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.05082501826765196</v>
+        <v>-0.06915132465199747</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7241989031037406</v>
+        <v>0.7048372525054134</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.538422247677623</v>
+        <v>0.519015773154436</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.006419959993507973</v>
+        <v>-0.0254757071337508</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.86675078713224</v>
+        <v>-0.8855039555963984</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.08428955194227683</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.417136130852946</v>
+        <v>-1.43552100073839</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.7029846211879089</v>
+        <v>-0.6898036118926711</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6458510165255547</v>
+        <v>-0.6326522775707915</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.109109964691648</v>
+        <v>-1.128170601366683</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.6899930707909547</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2676877778092503</v>
+        <v>-0.2873379913723682</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.181147639576551</v>
+        <v>-0.2010135613374473</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1020352603005108</v>
+        <v>0.1173506881442634</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.003339</t>
+          <t>X &gt; 0.003338</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01409947723476535</v>
+        <v>-0.03769510830448297</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.511804055798891</v>
+        <v>1.486410273096034</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3966710843671066</v>
+        <v>0.3718446170775209</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1507313610216343</v>
+        <v>0.1261102559247931</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5572199929537263</v>
+        <v>-0.5816183871497174</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.8835189929507976</v>
+        <v>0.8582372167469146</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.9609006677672127</v>
+        <v>-0.984969479005116</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5982085478765171</v>
+        <v>-0.5850275385812793</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.7283647272815017</v>
+        <v>-0.7151659883267385</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.578489912309429</v>
+        <v>-1.565084784656598</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.815055131509439</v>
+        <v>-0.8015978377992212</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.08910904193717784</v>
+        <v>-0.07565675321706777</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.01392694234063896</v>
+        <v>-0.01171355397169549</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.04336128169053666</v>
+        <v>-0.02359797007777331</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.004579</t>
+          <t>X &gt; 0.004578</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.07342191331908765</v>
+        <v>-0.1038668502064795</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.724216309847115</v>
+        <v>1.691326916598705</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.6356986535734706</v>
+        <v>0.6034384785104976</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4823461770472122</v>
+        <v>0.4502538538053926</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.257842960918623</v>
+        <v>-0.2896747599658198</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.9907111726465629</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.438951383902577</v>
+        <v>-1.469753654410908</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.164172705190268</v>
+        <v>-1.15099169589503</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.9778518988746256</v>
+        <v>-0.9646531599198624</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.498216160571971</v>
+        <v>-1.48481103291914</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.878567176563088</v>
+        <v>-0.8651098828528703</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1846621725564859</v>
+        <v>-0.1712098838363758</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.05460506315978364</v>
+        <v>0.06816110951138654</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.02109114693183045</v>
+        <v>0.04657606723998953</v>
       </c>
     </row>
     <row r="25">
@@ -3205,98 +3205,98 @@
         <v>984</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5904848344917397</v>
+        <v>0.5493869997686787</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.664218836056541</v>
+        <v>1.620739130193527</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.008731315649640692</v>
+        <v>-0.03343221280666597</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5156721319097741</v>
+        <v>-0.5572562675004136</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.303987808529904</v>
+        <v>-1.345242177495443</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1390620690726792</v>
+        <v>-0.1813202334031274</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.951438062767714</v>
+        <v>-1.938371808467238</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.707239347728084</v>
+        <v>-1.694058338432846</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.869865250170541</v>
+        <v>-1.856666511215778</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.110234337637493</v>
+        <v>-2.096829209984662</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.9938494505729594</v>
+        <v>-0.9803921568627416</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.4513362119267157</v>
+        <v>-0.4378839232066056</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.04304332346983841</v>
+        <v>0.05659936982144131</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.5202434743351674</v>
+        <v>-0.5306731100333195</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.007058</t>
+          <t>X &gt; 0.007057</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>788</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.5960950971922898</v>
+        <v>0.541753994654556</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.703068874906577</v>
+        <v>1.645602794434602</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.2409537470812637</v>
+        <v>0.1848436633639494</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3139167966341461</v>
+        <v>0.2577637717711667</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5354251480910079</v>
+        <v>-0.5911404495061205</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.4227895256365812</v>
+        <v>-0.4784257386690669</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.776558775903787</v>
+        <v>-1.763492521603311</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.116838621385796</v>
+        <v>-2.103657612090558</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.431645614167074</v>
+        <v>-2.418446875212311</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.393445926098558</v>
+        <v>-2.380040798445727</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.948453057522741</v>
+        <v>-0.9349957638125233</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.406455686979335</v>
+        <v>-0.3930033982592249</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.3154216817711912</v>
+        <v>0.3289777281227941</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.4500854123484572</v>
+        <v>-0.4605150480466094</v>
       </c>
     </row>
     <row r="27">
@@ -3309,98 +3309,98 @@
         <v>610</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.7861212470392402</v>
+        <v>-0.8575394071577236</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5219500439234181</v>
+        <v>-0.5961671642485911</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3400111454804389</v>
+        <v>-0.4152122705682046</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4480588797123417</v>
+        <v>-0.5230431445364729</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7345626338557878</v>
+        <v>-0.8099705975991185</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5122461287821238</v>
+        <v>-0.5877439209586868</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.072389682119976</v>
+        <v>-2.0593234278195</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.883835375983445</v>
+        <v>-1.870654366688207</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.944835262165746</v>
+        <v>-1.931636523210983</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.631026020964164</v>
+        <v>-2.617620893311333</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.115040326849396</v>
+        <v>0.1284976205596138</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.162051925641229</v>
+        <v>-1.148599636921119</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.5488410043974667</v>
+        <v>0.5623970507490696</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.332585204309844</v>
+        <v>-1.343014840007996</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.009537</t>
+          <t>X &gt; 0.009536</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>475</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.127106753165279</v>
+        <v>0.02954422051166716</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.8555360421889091</v>
+        <v>-0.842626232612858</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.040761142915478</v>
+        <v>-1.027754011497876</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.9105080103079786</v>
+        <v>-0.8975288679095144</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.9164520835800332</v>
+        <v>-1.016531209265167</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5053436266250984</v>
+        <v>-0.605967249570007</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1690247123184179</v>
+        <v>-0.1559584580179418</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.6269497836369098</v>
+        <v>0.6401307929321476</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.1448972658756631</v>
+        <v>0.1580960048304263</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1368773440056401</v>
+        <v>0.1502824716584712</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.090018756530164</v>
+        <v>3.103476050240381</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.019138755980848</v>
+        <v>1.032591044700958</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.704147302930693</v>
+        <v>2.717703349282296</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.4275528457332882</v>
+        <v>0.4171232100351361</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>366</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7223211539974415</v>
+        <v>-0.8504812479256643</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.426537818732811</v>
+        <v>-0.4136280091567599</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.366365653394801</v>
+        <v>-1.353358521977199</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.508592084819995</v>
+        <v>-1.495612942421531</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.681890684088351</v>
+        <v>-3.668779879713412</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.151590391077207</v>
+        <v>-2.281487593947539</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.8702038897702451</v>
+        <v>-0.8571376354697691</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2444911136883618</v>
+        <v>-0.231310104393124</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3054909998706634</v>
+        <v>-0.2922922609159002</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.155616184898591</v>
+        <v>-1.14221105724576</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.918319015373989</v>
+        <v>1.931776309084206</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.3133579104243367</v>
+        <v>0.3268101991444468</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.07889564920621</v>
+        <v>2.092451695557813</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4036234556759695</v>
+        <v>-0.4140530913741216</v>
       </c>
     </row>
     <row r="30">
@@ -3465,150 +3465,150 @@
         <v>297</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.7052148784432291</v>
+        <v>0.5392181976535682</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.4533524218563585</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-2.984729124619307</v>
+        <v>-2.971721993201704</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.181075318611136</v>
+        <v>-2.168096176212671</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.402998217184987</v>
+        <v>-4.389887412810047</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.095455269368315</v>
+        <v>-3.08241237307395</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.159986966438574</v>
+        <v>-1.146920712138098</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2803690184187246</v>
+        <v>-0.2671880091234868</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.3413689046010262</v>
+        <v>-0.328170165646263</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.5281944263293</v>
+        <v>-1.514789298676469</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.97075595305683</v>
+        <v>1.984213246767048</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.361864256601102</v>
+        <v>-1.348411967880992</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.09861718404432906</v>
+        <v>-0.08506113769272616</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.205798208670394</v>
+        <v>-2.216227844368547</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01326</t>
+          <t>X &gt; 0.01325</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>242</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4273226177306313</v>
+        <v>-0.4148003280550085</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.7992268092072905</v>
+        <v>-0.7863169996312394</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.326326920762554</v>
+        <v>-5.313319789344952</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-5.196073788155054</v>
+        <v>-5.18309464575659</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-7.387387565210695</v>
+        <v>-7.374276760835755</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-8.329615048982639</v>
+        <v>-8.316572152688273</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-5.108563642287976</v>
+        <v>-5.0954973879875</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.336077619581879</v>
+        <v>-4.322896610286641</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.39707750576418</v>
+        <v>-4.383878766809417</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-5.247202690792108</v>
+        <v>-5.233797563139277</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-1.719490456936661</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-5.00434971726839</v>
+        <v>-4.99089742854828</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.358488625733948</v>
+        <v>-3.344932579382345</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.761659855441138</v>
+        <v>-4.77208949113929</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.0145</t>
+          <t>X &gt; 0.01449</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>192</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.673228346456689</v>
+        <v>1.685750636132312</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4591785998408966</v>
+        <v>-0.4462687902648454</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.973794173829994</v>
+        <v>-6.96081503143153</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-9.595548722235492</v>
+        <v>-9.582437917860553</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-10.3397734511865</v>
+        <v>-10.32673055489214</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-6.25784050179211</v>
+        <v>-6.244774247491634</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-4.120857233906946</v>
+        <v>-4.107676224611708</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-4.181857120089248</v>
+        <v>-4.168658381134485</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-5.031982305117175</v>
+        <v>-5.018577177464344</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.070068962768083</v>
+        <v>-1.056611669057865</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.160685805422652</v>
+        <v>-4.147233516702542</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.539273749700889</v>
+        <v>-3.525717703349287</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.331219084091266</v>
+        <v>-4.341648719789418</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>142</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.14036449669144</v>
+        <v>3.152886786367063</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.8245655316145033</v>
+        <v>0.8374753411905544</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-7.186528915614026</v>
+        <v>-7.173549773215562</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-9.83762618702422</v>
+        <v>-9.824515382649281</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-13.76553636198462</v>
+        <v>-13.75249346569025</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-8.920692614468166</v>
+        <v>-8.90762636016769</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-7.979425309024315</v>
+        <v>-7.966244299729077</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-7.336199843093944</v>
+        <v>-7.32300110413918</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-7.482099676009192</v>
+        <v>-7.46869454835636</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.053050183425356</v>
+        <v>-2.039592889715138</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-5.539793786643315</v>
+        <v>-5.526341497923205</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.551597693362865</v>
+        <v>-4.538041647011262</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.301876361086578</v>
+        <v>-4.31230599678473</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>110</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.870198043426385</v>
+        <v>3.882720333102007</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.4533524218563585</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-6.318062457952642</v>
+        <v>-6.30505532653504</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.824172961708776</v>
+        <v>-9.811193819310311</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.36259417678095</v>
+        <v>-10.34948337240601</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-14.61060678451983</v>
+        <v>-14.59756388822547</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-13.7862495927012</v>
+        <v>-13.77318333840072</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-13.3443420823918</v>
+        <v>-13.33116107309656</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-11.58716015039228</v>
+        <v>-11.57396141143752</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-11.52819442632929</v>
+        <v>-11.51478929867646</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-8.062200956937808</v>
+        <v>-8.048748668217698</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-7.573364658791796</v>
+        <v>-7.559808612440193</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-8.232734235606422</v>
+        <v>-8.243163871304574</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>8.220847394075733</v>
+        <v>8.233369683751356</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2620241221339441</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-6.098524912711682</v>
+        <v>-6.085414108336742</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.37251154642459</v>
+        <v>-9.359468650130225</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-5.8858166922683</v>
+        <v>-5.872750437967824</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-8.73395247200218</v>
+        <v>-8.720771462706942</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-8.794952358184482</v>
+        <v>-8.781753619229718</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-7.264125162260029</v>
+        <v>-7.250720034607198</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-1.516497534196652</v>
+        <v>-1.503040240486435</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-5.053542948279798</v>
+        <v>-5.040090659559688</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-3.09284517827232</v>
+        <v>-3.079289131920717</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.033600036472215</v>
+        <v>-4.044029672170367</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY MA Ratio-20 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY MA Ratio-20 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.914535742698042</v>
+        <v>-2.901625933121991</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.560103697639512</v>
+        <v>-5.547124555241048</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.781571519621224</v>
+        <v>-2.768390510325986</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.4616190248511458</v>
+        <v>-0.4484202858963826</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>0.8779121404659378</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4785833931562493</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.109257106384923</v>
+        <v>3.098827470686771</v>
       </c>
     </row>
     <row r="7">
@@ -3963,98 +3963,98 @@
         <v>105</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.744656917885266</v>
+        <v>2.757179207560888</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1807023525400524</v>
+        <v>0.1936121621161035</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2141663540565375</v>
+        <v>-0.2011592226389354</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.893437030972848</v>
+        <v>-3.880457888574384</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.241382055568828</v>
+        <v>-8.228271251193888</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-6.039178213091262</v>
+        <v>-6.026135316796896</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.171530977982584</v>
+        <v>-5.158464723682108</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.829190567240275</v>
+        <v>-1.816009557945037</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.01457145133932869</v>
+        <v>0.02777019029409189</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.816835799136683</v>
+        <v>1.830293092846901</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.851218956482114</v>
+        <v>1.864671245202224</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.430964345537213</v>
+        <v>1.444520391888815</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.6806856778135</v>
+        <v>1.670256042115348</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01526</t>
+          <t>X &lt; -0.01525</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>145</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.299665128065882</v>
+        <v>1.312187417741505</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.377746687515419</v>
+        <v>0.3906564970914701</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.955834403715045</v>
+        <v>-1.942855261316581</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.114945273959634</v>
+        <v>-1.101834469584695</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.196813681071554</v>
+        <v>-2.183770784777188</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.591892225930046</v>
+        <v>-1.57882597162957</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.078855409771222</v>
+        <v>2.09203641906646</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>6.845441730485469</v>
+        <v>6.858640469440232</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.616006200629954</v>
+        <v>4.629411328282785</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.100908048726168</v>
+        <v>5.114365342436386</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.445636033657806</v>
+        <v>4.459088322377916</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>195</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6985665253381725</v>
+        <v>-0.6860442356625498</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.31014013830243</v>
+        <v>-2.297230328726378</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.910375770485587</v>
+        <v>1.923382901903189</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.036294173829987</v>
+        <v>-1.023315031431522</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.476566662379895</v>
+        <v>0.4896774667548343</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2611880872750447</v>
+        <v>0.2742309835694101</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.22773642128481</v>
+        <v>2.240802675585286</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.863117125067419</v>
+        <v>5.876298134362656</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.87904031580819</v>
+        <v>8.892239054762953</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.977633079498212</v>
+        <v>5.991038207151043</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.260059242360121</v>
+        <v>5.273516536070339</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.807262912526063</v>
+        <v>5.820715201246173</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.874187788760651</v>
+        <v>4.887743835112254</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.072627069754887</v>
+        <v>3.062197434056735</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>253</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.505296027719851</v>
+        <v>-1.492773738044228</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.697897308668303</v>
+        <v>-4.684987499092252</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3496830113123224</v>
+        <v>-0.3366758798947203</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.381485214673198</v>
+        <v>-3.368506072274734</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.548364927769086</v>
+        <v>-1.535254123394147</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4604091560613313</v>
+        <v>-0.4473662597669659</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.431141711646625</v>
+        <v>1.444207965947101</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.126013648833506</v>
+        <v>4.139194658128744</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.831812181623533</v>
+        <v>6.845010920578297</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.191173162603512</v>
+        <v>5.204578290256343</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.591162921289893</v>
+        <v>4.604620215000111</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.230289161639263</v>
+        <v>4.243741450359373</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.019520716702274</v>
+        <v>3.033076763053877</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.688214380994367</v>
+        <v>1.677784745296215</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>342</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.7229359487958789</v>
+        <v>0.7354582384715016</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.643023629080666</v>
+        <v>-2.630113819504615</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9911087099462605</v>
+        <v>-0.9781015785286584</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.907639203069756</v>
+        <v>-2.894660060671292</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2296861491360787</v>
+        <v>-0.2165753447611394</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.322203357857013</v>
+        <v>2.335269612157489</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.194201245625216</v>
+        <v>4.207382254920454</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>6.764780306811339</v>
+        <v>6.777979045766102</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>6.499450443420841</v>
+        <v>6.512855571073672</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.12510647582841</v>
+        <v>5.138563769538628</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.574694311536405</v>
+        <v>4.588146600256515</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.862042039772795</v>
+        <v>3.875598086124398</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.357377407136809</v>
+        <v>2.346947771438657</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>452</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.6039068125333955</v>
+        <v>0.6164291022090183</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5410057659408167</v>
+        <v>0.5539155755168679</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.916048563769003</v>
+        <v>1.929055695186605</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.603823820270307</v>
+        <v>1.616802962668771</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.056553047676012</v>
+        <v>3.069663852050951</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.238950737604064</v>
+        <v>4.251993633898429</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.260411710597268</v>
+        <v>5.273477964897744</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.120661940134354</v>
+        <v>6.133842949429592</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>8.272051434483032</v>
+        <v>8.285250173437795</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.8644041255613</v>
+        <v>7.877809253214132</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.217172925137525</v>
+        <v>7.230630218847743</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.587839268323656</v>
+        <v>6.601291557043766</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.282628905166362</v>
+        <v>5.296184951517965</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.311111299389559</v>
+        <v>5.300681663691407</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>540</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.8524173027989832</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.006099177936882</v>
+        <v>2.019008987512933</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.722341582451399</v>
+        <v>2.735348713869001</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.222965085429273</v>
+        <v>3.235944227827737</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.906766092579318</v>
+        <v>4.919876896954257</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.759763585850543</v>
+        <v>5.772806482144908</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.230585424133821</v>
+        <v>6.243651678434297</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>6.31895758090787</v>
+        <v>6.332138590203108</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>7.92462436139224</v>
+        <v>7.937823100347003</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>8.000425102290237</v>
+        <v>8.013830229943068</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7.425301407602291</v>
+        <v>7.438758701312508</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>7.644869750132898</v>
+        <v>7.658322038853008</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.483874398447263</v>
+        <v>6.497430444798866</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.363225360353177</v>
+        <v>6.352795724655024</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>674</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.957600255457677</v>
+        <v>1.9701225451333</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.978074120238233</v>
+        <v>1.990983929814284</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.918516986341942</v>
+        <v>2.931524117759544</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.048770118949442</v>
+        <v>3.061749261347906</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.697292524055307</v>
+        <v>3.710403328430246</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.181678081949016</v>
+        <v>5.194720978243382</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.283887984854779</v>
+        <v>6.296954239155255</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.816704586073278</v>
+        <v>5.829885595368516</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7.684488082680282</v>
+        <v>7.697686821635045</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>7.724570612785897</v>
+        <v>7.737975740438728</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>7.371449335946068</v>
+        <v>7.384906629656285</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.147672255902762</v>
+        <v>8.161124544622872</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>7.282313787391104</v>
+        <v>7.295869833742707</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.977138977234148</v>
+        <v>7.966709341535996</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>822</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.764469222369101</v>
+        <v>1.776991512044724</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.856058626436472</v>
+        <v>1.868968436012523</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.164352936871509</v>
+        <v>3.177360068289111</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.051297067045923</v>
+        <v>3.064276209444387</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.851075365355747</v>
+        <v>3.864186169730687</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.878444310370682</v>
+        <v>4.891487206665047</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6.01025560526385</v>
+        <v>6.023321859564327</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.637962717431257</v>
+        <v>6.651143726726495</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7.550198840981317</v>
+        <v>7.56339757993608</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.916618668118836</v>
+        <v>7.930023795771667</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.590210842584717</v>
+        <v>7.603668136294935</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>8.597830009662502</v>
+        <v>8.611282298382612</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.447648391418333</v>
+        <v>7.461204437769936</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>8.183987728560808</v>
+        <v>8.173558092862656</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>992</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.03478748624164</v>
+        <v>1.047309775917263</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.73369774424512</v>
+        <v>0.7466075538211712</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.153345166680793</v>
+        <v>2.166352298098396</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.981178944449574</v>
+        <v>1.994158086848039</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.753241600345156</v>
+        <v>2.766352404720095</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.655522247738233</v>
+        <v>3.668565144032598</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.276433691756274</v>
+        <v>4.28949994605675</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.918121260716717</v>
+        <v>4.931302270011955</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>6.167605245502152</v>
+        <v>6.180803984456915</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.42635102821616</v>
+        <v>6.439756155868992</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>6.524017058737293</v>
+        <v>6.537474352447511</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.96162602253434</v>
+        <v>6.97507831125445</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.432500443847495</v>
+        <v>5.446056490199098</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6.085447582575398</v>
+        <v>6.075017946877246</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1184</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7160211392494844</v>
+        <v>0.7285434289251072</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.6421740953363937</v>
+        <v>-0.6292642857603425</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9055247656345813</v>
+        <v>0.9185318970521834</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.146654534190354</v>
+        <v>-0.1336753917918898</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.088572899386129</v>
+        <v>1.101683703761069</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.554933756020709</v>
+        <v>1.567976652315075</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.976956795505195</v>
+        <v>1.990023049805671</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.269908531858825</v>
+        <v>2.283089541154062</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.137962699730579</v>
+        <v>3.151161438685342</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.554729406594539</v>
+        <v>3.56813453424737</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.856732839033711</v>
+        <v>3.870190132743929</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.397872753135907</v>
+        <v>4.411325041856017</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.964104628677489</v>
+        <v>2.977660675029092</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3.973961096088907</v>
+        <v>3.963531460390755</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>1406</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8493781805012546</v>
+        <v>0.8619004701768773</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.3354529004573052</v>
+        <v>-0.3225430908812541</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3365347229603302</v>
+        <v>0.3495418543779323</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3956641002335459</v>
+        <v>0.4086432426320101</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.06634672584417</v>
+        <v>1.079457530219109</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.64828368489696</v>
+        <v>1.661326581191325</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.705797478293235</v>
+        <v>1.718863732593711</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.807604122185992</v>
+        <v>1.82078513148123</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.386718034012226</v>
+        <v>2.399916772966989</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.030191711004214</v>
+        <v>3.043596838657045</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.394428429360879</v>
+        <v>3.407885723071097</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.357687831372033</v>
+        <v>3.371140120092143</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.510690688421448</v>
+        <v>2.524246734773051</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.973783286700574</v>
+        <v>2.963353651002421</v>
       </c>
     </row>
     <row r="19">
@@ -4587,150 +4587,150 @@
         <v>1682</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1819481244987102</v>
+        <v>0.194470414174333</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.353965474673565</v>
+        <v>0.3668752842496161</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6130801212279877</v>
+        <v>0.6260872526455898</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8622393180447645</v>
+        <v>0.8752184604432287</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.096707520332885</v>
+        <v>1.109818324707824</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.275243393839268</v>
+        <v>1.288286290133634</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.487774837090171</v>
+        <v>1.500841091390647</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.436762663041137</v>
+        <v>1.449943672336374</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.970293097905206</v>
+        <v>1.983491836859969</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.606493715493208</v>
+        <v>2.619898843146039</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.234082840640561</v>
+        <v>3.247540134350778</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.911747805358161</v>
+        <v>2.925200094078271</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.372587130203982</v>
+        <v>2.386143176555585</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.503402398271007</v>
+        <v>2.492972762572855</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003799</t>
+          <t>X &lt; -0.0003802</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1939</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5235807617910524</v>
+        <v>0.5361030514666751</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2013315428443363</v>
+        <v>0.2142413524203874</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3737655696154647</v>
+        <v>0.3867727010330668</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6587376295050689</v>
+        <v>0.6717167719035331</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9454840266041131</v>
+        <v>0.9585948309790524</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6240502551913565</v>
+        <v>0.6370931514857219</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.51920307737241</v>
+        <v>1.532269331672886</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.206738605873014</v>
+        <v>1.219919615168251</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.455176574254914</v>
+        <v>1.468375313209677</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.945948759005226</v>
+        <v>1.959353886658057</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.050633289251856</v>
+        <v>2.064090582962073</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.930297519315182</v>
+        <v>1.943749808035292</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.510042908370281</v>
+        <v>1.523598954721884</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.656618289125163</v>
+        <v>1.646188653427011</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0008597</t>
+          <t>X &lt; 0.0008593</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2206</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.3145326942827751</v>
+        <v>0.3270549839583978</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.3459539621597401</v>
+        <v>-0.3330441525836889</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.152054552814306</v>
+        <v>-0.1390474213967039</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.0687782899381304</v>
+        <v>0.0817574323365946</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6626034516775547</v>
+        <v>0.675714256052494</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2354077082337938</v>
+        <v>0.2484506045281591</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.192340657628179</v>
+        <v>1.205406911928655</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.112963185969207</v>
+        <v>1.100657108721627</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.9414807463356567</v>
+        <v>0.9292309105133114</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.451283031842635</v>
+        <v>1.464688159495466</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.291860623209544</v>
+        <v>1.305317916919762</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.9635964550790064</v>
+        <v>0.9770487437991164</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9059891696100735</v>
+        <v>0.9195452159616764</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9290559234638849</v>
+        <v>0.9186262877657327</v>
       </c>
     </row>
     <row r="22">
@@ -4743,150 +4743,150 @@
         <v>2470</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.05510536911041441</v>
+        <v>0.06762765878603716</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3833290852778006</v>
+        <v>-0.3704192757017495</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3736670475378148</v>
+        <v>-0.3606599161202126</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.03975760610528312</v>
+        <v>0.05273674850374732</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.634022475175513</v>
+        <v>0.6471332795504523</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1224029242180364</v>
+        <v>0.1354458205124018</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.089449142220836</v>
+        <v>1.102515396521312</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.5639026473826902</v>
+        <v>0.5545406038672596</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5659498974546082</v>
+        <v>0.5565709457237418</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.889913781252595</v>
+        <v>0.9033189089054261</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6041887970159863</v>
+        <v>0.617646090726204</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3146853146853132</v>
+        <v>0.3281376034054233</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2588031733760303</v>
+        <v>0.2723592197276332</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.02269454613814759</v>
+        <v>0.01226491043999545</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.003339</t>
+          <t>X &lt; 0.003338</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2714</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.02587024911698421</v>
+        <v>0.03839253879260696</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.7030259089006066</v>
+        <v>-0.6901160993245554</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.2152171605505231</v>
+        <v>-0.202210029132921</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.04818580065357736</v>
+        <v>-0.03520665825511315</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3328486665103654</v>
+        <v>0.3459594708853047</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3994997598784167</v>
+        <v>-0.3864568635840513</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.6191133415326391</v>
+        <v>0.6321795958331151</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3930316549819466</v>
+        <v>0.3857803157830446</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.4997003575208581</v>
+        <v>0.492397542338658</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.9587516173177804</v>
+        <v>0.9511657988575806</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.5540102269188409</v>
+        <v>0.546542479199374</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1671820403154953</v>
+        <v>0.1598567227081418</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1153872672482663</v>
+        <v>0.1289433135998692</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.1071867130101793</v>
+        <v>0.09675707731202721</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.004579</t>
+          <t>X &lt; 0.004578</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2946</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.04721208629408835</v>
+        <v>0.0597343759697111</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6158520415753159</v>
+        <v>-0.6029422319992648</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2654632955973781</v>
+        <v>-0.252456164179776</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1690855017432753</v>
+        <v>-0.1561063593448111</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1393767520192455</v>
+        <v>0.1524875563941848</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3423141015929971</v>
+        <v>-0.3292712052986317</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.6908383599965049</v>
+        <v>0.7039046142969809</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5474049371085314</v>
+        <v>0.5417140192907297</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.5052897725661225</v>
+        <v>0.4996037898809931</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7252659146183333</v>
+        <v>0.7194171728181473</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4719369169243635</v>
+        <v>0.4661502841466145</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1862489304669452</v>
+        <v>0.1805593372097078</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.09064817833712624</v>
+        <v>0.08494568314544892</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.06881486024003181</v>
+        <v>0.05838522454187967</v>
       </c>
     </row>
     <row r="25">
@@ -4896,101 +4896,101 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3174</v>
+        <v>3175</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1678569248611339</v>
+        <v>-0.1553346351855112</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4280791864740436</v>
+        <v>-0.4151693768979925</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.00585172713726223</v>
+        <v>0.007155404280339894</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1872549566958881</v>
+        <v>0.2002340990943523</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4345031319442612</v>
+        <v>0.4476139363192004</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.1034095574034879</v>
+        <v>0.1164524536978533</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.6960458546995554</v>
+        <v>0.691704382300955</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5921930805584665</v>
+        <v>0.5878466717521249</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6745573708408088</v>
+        <v>0.6701780968529434</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.7545448608152796</v>
+        <v>0.7500738658406831</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4102977353748187</v>
+        <v>0.4059171750789048</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2421269569618971</v>
+        <v>0.2377995333446776</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.0916317621101328</v>
+        <v>0.0873175611343342</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2332106575596455</v>
+        <v>0.2364352697118974</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.007058</t>
+          <t>X &lt; 0.007057</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1251730745024489</v>
+        <v>-0.1126507848268261</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3157875400422014</v>
+        <v>-0.3028777304661503</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.05938330406922177</v>
+        <v>-0.04637617265161964</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.04754343374710146</v>
+        <v>-0.03456429134863725</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.154118240464328</v>
+        <v>0.1672290448392673</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1555270224665506</v>
+        <v>0.168569918760916</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5015798417080362</v>
+        <v>0.4983059774935654</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.5543007439761567</v>
+        <v>0.5509828416206517</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6579576947255674</v>
+        <v>0.6546038621514541</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.6542704117372011</v>
+        <v>0.6508672669801001</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.3180993344944909</v>
+        <v>0.3147823242240904</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1913308019320326</v>
+        <v>0.1880515905214892</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.02513592101996664</v>
+        <v>0.02188016141939642</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.1729846745635228</v>
+        <v>0.1754332539077978</v>
       </c>
     </row>
     <row r="27">
@@ -5000,101 +5000,101 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3548</v>
+        <v>3549</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1499812523434514</v>
+        <v>0.1625035420190741</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1694537586143028</v>
+        <v>0.1823635681903539</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.05579990016168068</v>
+        <v>0.06880703157928281</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.101688578325998</v>
+        <v>0.1146677207244622</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1538185443561844</v>
+        <v>0.1669293487311236</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1419241491134642</v>
+        <v>0.1549670454078296</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.4382741254934004</v>
+        <v>0.4358359887288401</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.3805261838383132</v>
+        <v>0.3780832690591822</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.4195947046597865</v>
+        <v>0.417136966830256</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5423420192071546</v>
+        <v>0.5398124463277583</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.07192155633451591</v>
+        <v>0.06951445706825865</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2911921288496444</v>
+        <v>0.2887234907132097</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.0004247781596120603</v>
+        <v>-0.002830379405629913</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2934520921582617</v>
+        <v>0.295220820926275</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.009537</t>
+          <t>X &lt; 0.009536</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3683</v>
+        <v>3684</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.002913144248950061</v>
+        <v>0.009609145426672683</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1868916682338337</v>
+        <v>0.1851041568566103</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1317553298933163</v>
+        <v>0.1299691669784906</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1413451289786423</v>
+        <v>0.1395596525699219</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1447824888184215</v>
+        <v>0.1578932931933608</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.117109281586913</v>
+        <v>0.1301521778812784</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.101407465687565</v>
+        <v>0.09962767610630863</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.02563043350937022</v>
+        <v>-0.02739167176617485</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.06389486834169844</v>
+        <v>0.06210650546531582</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.06955688663764903</v>
+        <v>0.0677388022898171</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3098727247503632</v>
+        <v>-0.3115953956648667</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.04320502749411048</v>
+        <v>-0.04499983972660004</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2581934022524592</v>
+        <v>-0.259944297650506</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.006843183987292889</v>
+        <v>0.008242702577575756</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3792</v>
+        <v>3793</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.0827972213252437</v>
+        <v>0.09531951100086644</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1153404202309787</v>
+        <v>0.1139967197246321</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.1292619167783613</v>
+        <v>0.1279042986412549</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1686518929945322</v>
+        <v>0.1672864064082091</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.3814249619750285</v>
+        <v>0.3799897327577</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2578142681117441</v>
+        <v>0.2708571644061095</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1612006932592251</v>
+        <v>0.1598310156662563</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.07707588878921712</v>
+        <v>0.07571633483376417</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1096339693673372</v>
+        <v>0.108263683109854</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1961086678368176</v>
+        <v>0.1946942649024379</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.09921916039653667</v>
+        <v>-0.100561440747363</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.05540099830252387</v>
+        <v>0.05401813020127122</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.1127314349104864</v>
+        <v>-0.1140809084099104</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.09916066274418256</v>
+        <v>0.1001959062761415</v>
       </c>
     </row>
     <row r="30">
@@ -5156,153 +5156,153 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3861</v>
+        <v>3862</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.04119257937362875</v>
+        <v>-0.028670289698006</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.03906242778626279</v>
+        <v>0.03799596623145618</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2263590296506592</v>
+        <v>0.2252359675052844</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.1899178299588726</v>
+        <v>0.1888061806896815</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3632691072218748</v>
+        <v>0.3621016068100715</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2872996512516863</v>
+        <v>0.2861570420070976</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.165052466149973</v>
+        <v>0.1639392443667305</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.07409363239769107</v>
+        <v>0.07299423385089199</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1049811278845425</v>
+        <v>0.1038720041771271</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2006071731061922</v>
+        <v>0.1994561041359333</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.06722217187781609</v>
+        <v>-0.06830852114929087</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1888050911171675</v>
+        <v>0.1876526116618464</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.09388264594903006</v>
+        <v>0.09274592595436104</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2288042259320449</v>
+        <v>0.2296010644329129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01326</t>
+          <t>X &lt; 0.01325</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3916</v>
+        <v>3917</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.03901268513489242</v>
+        <v>0.0381679389313021</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1210573132616162</v>
+        <v>0.1201656290106285</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3256859505016436</v>
+        <v>0.3247354529502431</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3425477348132446</v>
+        <v>0.3415945687721944</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.480486309611635</v>
+        <v>0.479488979745156</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.5626857740938291</v>
+        <v>0.561671780564339</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.3900533294594837</v>
+        <v>0.3890815119375191</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.3193730907573453</v>
+        <v>0.3184113784131881</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.3490342341571235</v>
+        <v>0.3480635294553522</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.405942864950859</v>
+        <v>0.4049436080495568</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1900845627911565</v>
+        <v>0.1891366302618636</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.3920196565477312</v>
+        <v>0.391020289540549</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2925809860662838</v>
+        <v>0.2915998055838429</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.3525568777745818</v>
+        <v>0.3531644875971907</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.0145</t>
+          <t>X &lt; 0.01449</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3966</v>
+        <v>3967</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.06820584974001065</v>
+        <v>-0.06885572902681503</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.09307755903290627</v>
+        <v>0.0923663358137361</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2147283619892946</v>
+        <v>0.2139811925014854</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3587427141646486</v>
+        <v>0.3579606369952586</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.4881776928588479</v>
+        <v>0.487355844714898</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.5479236633915932</v>
+        <v>0.5470901998248507</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.3763937040976444</v>
+        <v>0.3756019477776178</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.2503663310477364</v>
+        <v>0.2495999730558793</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2788685577416956</v>
+        <v>0.2780938847265446</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3243359148660403</v>
+        <v>0.3235385784325828</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.1337922113311834</v>
+        <v>0.1330398842586789</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2831986031794997</v>
+        <v>0.2824087105587267</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2553128396613502</v>
+        <v>0.2545242321345853</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2672428422829114</v>
+        <v>0.2677328447849803</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4016</v>
+        <v>4017</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.098303050912385</v>
+        <v>-0.0987820354971376</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.04096621975526205</v>
+        <v>0.04043696798781582</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1561908774876883</v>
+        <v>0.1556289742684243</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2751812360060839</v>
+        <v>0.2745907710682758</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.3714543833545747</v>
+        <v>0.3708345610266761</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.5335284043469599</v>
+        <v>0.5328708943832297</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.3879306888616298</v>
+        <v>0.3873082574785514</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.3322548164825818</v>
+        <v>0.3316414487663764</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.3347950394067354</v>
+        <v>0.3341801734817977</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.3442614759773619</v>
+        <v>0.3436357878013467</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1535459497308764</v>
+        <v>0.1529654453700005</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2766379045491334</v>
+        <v>0.2760268299840263</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2438666535851439</v>
+        <v>0.2432593996870551</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2089535586710198</v>
+        <v>0.2093221539969932</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4048</v>
+        <v>4049</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.09255183904769382</v>
+        <v>-0.0929298168465067</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.05754964318045097</v>
+        <v>0.05712220538483592</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1687569556960398</v>
+        <v>0.1682989054398902</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2878392252171551</v>
+        <v>0.2873526206995436</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3051630105719951</v>
+        <v>0.3046677992414644</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.443633846643877</v>
+        <v>0.4431065579170053</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.4464597448170196</v>
+        <v>0.4459308807134974</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.4122170959730127</v>
+        <v>0.4116928670446924</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3896022926914142</v>
+        <v>0.3890829443054145</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3922937725399578</v>
+        <v>0.3917670120249213</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.250849740432777</v>
+        <v>0.2503560834923206</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2991907377872209</v>
+        <v>0.298685186498318</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2880601599064221</v>
+        <v>0.2875539015889856</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2801116141959525</v>
+        <v>0.2803772948644081</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1567610508192203</v>
+        <v>-0.1570412751527499</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.006588654197280164</v>
+        <v>0.006258532139526096</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.00783657612333144</v>
+        <v>-0.008165725680676417</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1112735702118002</v>
+        <v>0.1109158947210673</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1495069965987028</v>
+        <v>0.1491365189660883</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2399566647697355</v>
+        <v>0.239565673371402</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1931672169042926</v>
+        <v>0.192786996996368</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2296329621714932</v>
+        <v>0.2292407891920973</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2557603515132669</v>
+        <v>0.2553612267086578</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2284599051165941</v>
+        <v>0.2280621132114788</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1110997887649106</v>
+        <v>0.1107293477804561</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1838513224805212</v>
+        <v>0.1834630739278182</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1455422012193637</v>
+        <v>0.145160608721369</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1392031054030838</v>
+        <v>0.1394351247913548</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_20.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_20.xlsx
@@ -575,46 +575,46 @@
         <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>14.14045182436563</v>
+        <v>14.11147353050631</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12.53783271752867</v>
+        <v>12.53674760160194</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.59841483563831</v>
+        <v>-11.59865190009933</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.779686108111434</v>
+        <v>2.779209574934136</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-21.51356710046309</v>
+        <v>-21.46526159192733</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.7170197124729</v>
+        <v>-11.69317450243201</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.050761567914755</v>
+        <v>-7.00286897118572</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.990725888347505</v>
+        <v>2.039906134458391</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.930254761358292</v>
+        <v>2.003425464998791</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.08160180353093</v>
+        <v>1.180851568021787</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.635692082650145</v>
+        <v>5.735535597497069</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.671427120218276</v>
+        <v>5.795068770249877</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>5.252766153288057</v>
+        <v>5.401421611723293</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.044029672172535</v>
+        <v>-3.872030912601545</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.473097524407095</v>
+        <v>-2.502217230596692</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.9053834772504885</v>
+        <v>0.9042066620964704</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>20.45707307396859</v>
+        <v>20.4570728671476</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.135842555853728</v>
+        <v>3.135368983271547</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>17.56620677140466</v>
+        <v>17.61474558575672</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.887121523693231</v>
+        <v>7.911070634267652</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.804474250498821</v>
+        <v>7.852435204910748</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>12.33236801233146</v>
+        <v>12.38158953896028</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>24.75892669746608</v>
+        <v>24.83217380541431</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13.92592975957089</v>
+        <v>14.02521303428431</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>13.7248218063928</v>
+        <v>13.8246810253834</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.26383669947574</v>
+        <v>11.38748524308155</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.347213912522207</v>
+        <v>8.495871013846902</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.575017946877246</v>
+        <v>8.747016706442771</v>
       </c>
     </row>
     <row r="8">
@@ -679,150 +679,150 @@
         <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.459845408353793</v>
+        <v>-6.488999950381434</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-10.06147424304987</v>
+        <v>-10.06274227156486</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.463944487688842</v>
+        <v>-8.464159200363426</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.639447030652939</v>
+        <v>1.638963980922455</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.093642719562631</v>
+        <v>5.142105621535144</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.387781565755233</v>
+        <v>7.411728665957114</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13.29447862340642</v>
+        <v>13.34246604358644</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>16.82515239049894</v>
+        <v>16.8743932661912</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>14.77082708977477</v>
+        <v>14.8440410810182</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.92964841489723</v>
+        <v>10.02891996059485</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.730639556026958</v>
+        <v>5.830481583267577</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.764466129492455</v>
+        <v>9.888111844162289</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.346914756263473</v>
+        <v>9.495571950779087</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.575017946877239</v>
+        <v>1.747016706444818</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.0134</t>
+          <t>X ≈ -0.01339</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>58</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.190952101750099</v>
+        <v>-4.220086004687204</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-12.67329302355342</v>
+        <v>-12.67458812098197</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-7.913137539260234</v>
+        <v>-7.913351369493476</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-11.22427940749158</v>
+        <v>-11.22485409010761</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-8.324032582710728</v>
+        <v>-8.275657702153204</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.867481574855084</v>
+        <v>-2.843592487789593</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.231855435552497</v>
+        <v>-1.183939858087754</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.698822300790837</v>
+        <v>-1.649659417980189</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.03832333039419922</v>
+        <v>0.0348377668030011</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.557608045863191</v>
+        <v>2.656857109049113</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.353800703483266</v>
+        <v>2.45363397680606</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.057716102427825</v>
+        <v>-0.9340869587261409</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.20166220230174</v>
+        <v>-3.053014735486578</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.976706191053793</v>
+        <v>-2.804707431486342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01216</t>
+          <t>X ≈ -0.01215</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>89</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.04601965756315</v>
+        <v>7.016996170066648</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.202378175963077</v>
+        <v>3.201217547271227</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.793375059607207</v>
+        <v>-2.793551357061745</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.542988740243423</v>
+        <v>-1.543496992410198</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.524012095436326</v>
+        <v>3.572458393629937</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.942801751542035</v>
+        <v>4.966734504568535</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.859342375677336</v>
+        <v>4.907286073725366</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.393972727088695</v>
+        <v>4.443159593228373</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.57833246461071</v>
+        <v>6.65151479884824</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>10.22091322419658</v>
+        <v>10.32018188431503</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.651007075869749</v>
+        <v>6.750847393055352</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.564170060427713</v>
+        <v>5.68780653108012</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.268959106828916</v>
+        <v>6.417611999782373</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.249175250247525</v>
+        <v>4.421174009814187</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>110</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2453115446366496</v>
+        <v>0.2162306726659509</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>10.42061837157431</v>
+        <v>10.41952945456841</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.9354738171773</v>
+        <v>10.93541518610223</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>15.6020228693666</v>
+        <v>15.60164961121643</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>13.25480884343548</v>
+        <v>13.30332081961895</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>14.46205838149879</v>
+        <v>14.48605208212837</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>14.38122910857601</v>
+        <v>14.42922368929746</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>12.10327125281733</v>
+        <v>12.1524928820854</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>12.95331101338689</v>
+        <v>13.02651619874921</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>12.10797105359877</v>
+        <v>12.20724326727958</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>13.72364533644124</v>
+        <v>13.82349980886042</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>12.85323184885399</v>
+        <v>12.97687720915723</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>9.710229109086825</v>
+        <v>9.858883051839136</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>14.48410885596856</v>
+        <v>14.6561076155344</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>88</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.056928576542219</v>
+        <v>2.027873772999534</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9.512746892103998</v>
+        <v>9.511659612776526</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.855205158899864</v>
+        <v>6.855119534556941</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>11.52013168842382</v>
+        <v>11.51973777295692</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>14.38660318156591</v>
+        <v>14.43512712297285</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>13.55326467027898</v>
+        <v>13.57725944748159</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11.20405692559216</v>
+        <v>11.25203652378853</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>7.337345073653658</v>
+        <v>7.386544715355996</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.14354278494249</v>
+        <v>6.216719681301342</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.70190054566342</v>
+        <v>8.801159524201211</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>8.500078491352056</v>
+        <v>8.599918823860648</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>13.07999024221997</v>
+        <v>13.20363436575366</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>12.66381128280599</v>
+        <v>12.81246620222959</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>11.75683612869542</v>
+        <v>11.92883488826261</v>
       </c>
     </row>
     <row r="13">
@@ -939,930 +939,930 @@
         <v>134</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6.449826440079306</v>
+        <v>6.420833445070954</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.870838579476157</v>
+        <v>1.86968138105199</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.709081136976316</v>
+        <v>3.708972962214169</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.351708681189955</v>
+        <v>2.351245050425696</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.16241414317463</v>
+        <v>-1.114010290926608</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.856713461162393</v>
+        <v>2.880639719898625</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.497000668511831</v>
+        <v>6.544953097210083</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.797814839364598</v>
+        <v>3.846994965610087</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>6.718757385909811</v>
+        <v>6.791933744020632</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.617458763404549</v>
+        <v>6.71670673777944</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7.160849148300308</v>
+        <v>7.260683103735715</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>10.18089691985994</v>
+        <v>10.30453400709424</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>10.51019384563736</v>
+        <v>10.65884535484215</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>14.47054033493695</v>
+        <v>14.64253909450344</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.007198</t>
+          <t>X ≈ -0.007199</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>148</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.892561604700596</v>
+        <v>0.863521540986433</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.307511307708559</v>
+        <v>1.306351954962814</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.280926041769014</v>
+        <v>4.280831433813766</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.064904766064927</v>
+        <v>3.064452959536553</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.550394158496893</v>
+        <v>4.598836236415799</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.499882454500792</v>
+        <v>3.523813478929213</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.764816970150243</v>
+        <v>4.812756593422826</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>10.3706317822134</v>
+        <v>10.41984723341213</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.939342689001926</v>
+        <v>7.012516449408515</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>8.792400284570135</v>
+        <v>8.891650914379227</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.590997402409712</v>
+        <v>8.690831297554709</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>10.65404999440467</v>
+        <v>10.77768479015713</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>8.211292387208218</v>
+        <v>8.359939337598</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>9.115558487417779</v>
+        <v>9.287557246984598</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.005958</t>
+          <t>X ≈ -0.005959</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>170</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.472495867200195</v>
+        <v>-2.501566331299195</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.664084144682768</v>
+        <v>-4.665316780752356</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.715456179796597</v>
+        <v>-2.715623211642573</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.172454622818535</v>
+        <v>-3.172966358113584</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.537400523509213</v>
+        <v>-2.489033431884351</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.2418511246767</v>
+        <v>-2.217969113793231</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.088081590824828</v>
+        <v>-4.040212452754098</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.381214517251351</v>
+        <v>-3.332085147492478</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.5064364355464051</v>
+        <v>-0.4333072911094931</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.7674996311949229</v>
+        <v>-0.6682961633870974</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.379127031681378</v>
+        <v>1.478932989330374</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.9371347637131535</v>
+        <v>-0.813528944310292</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.296968389109466</v>
+        <v>-4.148338374234669</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.07204087665216</v>
+        <v>-3.900042117085498</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.004719</t>
+          <t>X ≈ -0.00472</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>192</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.9157737791387746</v>
+        <v>-0.9448079222700514</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-7.707428798793799</v>
+        <v>-7.708719268351992</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.510676805988318</v>
+        <v>-5.510886416912356</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-11.09219780038067</v>
+        <v>-11.09281281008161</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.478999720044179</v>
+        <v>-7.430711203010425</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-9.263074452023957</v>
+        <v>-9.239272164066776</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-9.870320055420279</v>
+        <v>-9.82252082433385</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-11.37937320829938</v>
+        <v>-11.33031897384752</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-12.4840975320099</v>
+        <v>-12.41105701699779</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-11.25601552572989</v>
+        <v>-11.15688074098345</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-9.902751875118682</v>
+        <v>-9.80299881078551</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-8.830196237115949</v>
+        <v>-8.706620645768801</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-9.772970557834952</v>
+        <v>-9.624354898499398</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-6.945815386456083</v>
+        <v>-6.77381662688942</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.003479</t>
+          <t>X ≈ -0.003481</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>222</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.564465628991485</v>
+        <v>1.535500403653401</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.309095615028113</v>
+        <v>1.307927239405124</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.675848973689746</v>
+        <v>-2.676032720996986</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.289359648715561</v>
+        <v>3.288912762586868</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.9564692945828739</v>
+        <v>1.004816781633544</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.151319781202574</v>
+        <v>2.175217403816795</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2702349058748013</v>
+        <v>0.3180926404494073</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.645259997116284</v>
+        <v>-0.596153680910291</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.605893309533116</v>
+        <v>-1.532817382353421</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2438043697166563</v>
+        <v>0.3429662590147444</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9396804771306506</v>
+        <v>1.039452526571921</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.176127243325119</v>
+        <v>-2.052553256205456</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1056110215384862</v>
+        <v>0.2542282494582224</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.370927999068698</v>
+        <v>-2.198929239502036</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.00224</t>
+          <t>X ≈ -0.002243</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>276</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.19101159213254</v>
+        <v>-3.220033009508136</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.861493482165535</v>
+        <v>3.860386903347269</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.025066494151496</v>
+        <v>2.024960426928942</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.238261775622334</v>
+        <v>3.237833785592571</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.258043582031412</v>
+        <v>1.306360260960091</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6125859872885755</v>
+        <v>-0.5887326574455187</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3869222331729816</v>
+        <v>0.4347528623468122</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4402010499154656</v>
+        <v>-0.3911203729909118</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1398260095491821</v>
+        <v>-0.06677395217475635</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4584366048323716</v>
+        <v>0.5575649705962604</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.425806477994826</v>
+        <v>2.525561581353564</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.6516709444656783</v>
+        <v>0.7752301489889888</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.681465347732527</v>
+        <v>1.830071297816197</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.09675707731202721</v>
+        <v>0.2687558368786895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001</t>
+          <t>X ≈ -0.001003</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>257</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.755215546748822</v>
+        <v>2.911794693839077</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7812143983526525</v>
+        <v>-0.7824044810107438</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.175772301630722</v>
+        <v>-1.175933390120356</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6596872578641495</v>
+        <v>-0.660169370363505</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.03387187282676507</v>
+        <v>0.01437213064421172</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.614639467605542</v>
+        <v>-3.590863438559957</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.729673584097441</v>
+        <v>1.777485760291583</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2871871300643889</v>
+        <v>-0.2381429984015</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.901400982525637</v>
+        <v>-1.828415001502833</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.362456140606348</v>
+        <v>-2.263401393216235</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.676415767339833</v>
+        <v>-5.576745269558131</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.477230638189354</v>
+        <v>-4.353724842927157</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.120347848225052</v>
+        <v>-3.971773379955778</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.895799173745409</v>
+        <v>-3.723800414178655</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002395</t>
+          <t>X ≈ 0.0002356</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.181161748229286</v>
+        <v>-0.6587813693095796</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.287923071371225</v>
+        <v>-4.102796610017599</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.939548533437922</v>
+        <v>-3.924537442108935</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.183031824956409</v>
+        <v>-4.337805497567629</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.365571266244324</v>
+        <v>-1.485172478120056</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.562136931602481</v>
+        <v>-2.698920228931804</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.150422067400122</v>
+        <v>-1.275919724129828</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2475768890256234</v>
+        <v>0.1203309834514101</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.974616227492902</v>
+        <v>-3.26613733372357</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.126507160348389</v>
+        <v>-2.600736441247911</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.201107391739491</v>
+        <v>-4.66801494947935</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.038704306213816</v>
+        <v>-6.475089520961752</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.466026690495163</v>
+        <v>-3.888771567696388</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-4.365056959489792</v>
+        <v>-4.760445980123251</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.001479</t>
+          <t>X ≈ 0.001475</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.090741825321864</v>
+        <v>-2.310222295068819</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6759411764685126</v>
+        <v>-0.5025166348737855</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.201608795218824</v>
+        <v>-2.02140527223488</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1893105874771663</v>
+        <v>-0.01755604912715825</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4034723982384065</v>
+        <v>0.6181135331678504</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8074633681922947</v>
+        <v>-0.6093429329767019</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2376844965222773</v>
+        <v>0.4531249891786189</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.006186867294815</v>
+        <v>-3.770131973139499</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.554872936411208</v>
+        <v>-2.30280617893019</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.782081015001097</v>
+        <v>-3.503376392700417</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.121803464311043</v>
+        <v>-4.838089318574134</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.089285704493363</v>
+        <v>-4.781652277791459</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.133040828614014</v>
+        <v>-4.801647858583742</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-7.561345689486259</v>
+        <v>-7.196379519971188</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.002718</t>
+          <t>X ≈ 0.002713</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2554391632673685</v>
+        <v>-0.2822019386722445</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.923740676811946</v>
+        <v>-3.859785430272723</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.390582660577209</v>
+        <v>1.377300276382051</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.9231876604927436</v>
+        <v>-0.9097469878828974</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.685154145782718</v>
+        <v>-2.609382976627238</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.666056686187666</v>
+        <v>-5.55577547196097</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.103746201167034</v>
+        <v>-4.014825738286568</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.310301259167112</v>
+        <v>-1.251896585715535</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1439952610038731</v>
+        <v>-0.07849364307634943</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.459292492296946</v>
+        <v>1.521474747771236</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1633192626455227</v>
+        <v>-0.2956052191444414</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.540942045201895</v>
+        <v>-1.853855508988602</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.322073031187855</v>
+        <v>-1.845128229219469</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9520671272050691</v>
+        <v>0.4271786497637464</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.003958</t>
+          <t>X ≈ 0.003952</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>232</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3082804215537323</v>
+        <v>0.07482278262508402</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4150142016789999</v>
+        <v>0.2268165349682292</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8390319084319984</v>
+        <v>-1.027545290558344</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.568657779545781</v>
+        <v>-1.7555004539404</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.108030541348214</v>
+        <v>-2.248518263060156</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3366762315857059</v>
+        <v>0.1719392090459166</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.549699507060566</v>
+        <v>1.386129102955294</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.374086783925527</v>
+        <v>2.213283457889119</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5892647838390772</v>
+        <v>0.4611657741194435</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.984791943525266</v>
+        <v>-2.080224858223936</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4695283953420457</v>
+        <v>-0.5623441218727336</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4239378478226357</v>
+        <v>0.3578078363420616</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4293341005448994</v>
+        <v>-0.4672417281646659</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3904992945021135</v>
+        <v>-0.6495350176940278</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.005198</t>
+          <t>X ≈ 0.005192</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.910861559270039</v>
+        <v>-2.946861080387706</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.994638627614854</v>
+        <v>1.993910804481899</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.340035684868958</v>
+        <v>3.776045389810051</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.779467650158708</v>
+        <v>5.211351379031512</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.246038510117756</v>
+        <v>4.291933656013555</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.853550227685922</v>
+        <v>5.675744150091582</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5438719507918108</v>
+        <v>0.1781992802985997</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.182534837979226</v>
+        <v>1.026637896211305</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.868277572286132</v>
+        <v>2.738543555078543</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.144996330541439</v>
+        <v>1.482855283741991</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.36974849584103</v>
+        <v>-0.02741154693077874</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.9746733246365693</v>
+        <v>1.346046990963153</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1178412486158322</v>
+        <v>0.5149691980055096</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.526983012379432</v>
+        <v>2.518946531005263</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.006438</t>
+          <t>X ≈ 0.006431</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5800747958397778</v>
+        <v>0.9881987824983867</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.520777051510017</v>
+        <v>1.905409519835267</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9109903272068891</v>
+        <v>-0.4856874918949075</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.833969486612617</v>
+        <v>-3.346734079801763</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.377038920636203</v>
+        <v>-3.571269883247886</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.013165165319137</v>
+        <v>1.69139489157044</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.641457920960967</v>
+        <v>-1.870955185060055</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.04730207495185113</v>
+        <v>0.1618782974387898</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4019198501580661</v>
+        <v>0.6257283971588308</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.9582030278044158</v>
+        <v>-1.192582587369998</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.162904186064608</v>
+        <v>-1.390200405526485</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6183219520766343</v>
+        <v>-0.8299542211652309</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.038472805390157</v>
+        <v>-1.224291360094277</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.8127371551635107</v>
+        <v>-0.9766013840082906</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.007677</t>
+          <t>X ≈ 0.007671</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.337085315471924</v>
+        <v>5.335032291877106</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>9.328072877562406</v>
+        <v>9.357674539075987</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.241215122344919</v>
+        <v>2.804711823189763</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.933562754623168</v>
+        <v>3.494108951552029</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1587830917114559</v>
+        <v>0.7647715646995508</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1037960128451019</v>
+        <v>0.4780439963708858</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.7496899778287158</v>
+        <v>-0.1472149232778506</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.90215188004241</v>
+        <v>-2.554439040452138</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4.086729542183136</v>
+        <v>-3.715286009754386</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.565861821659134</v>
+        <v>-1.167750041123305</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.579551743964231</v>
+        <v>-4.172505067046991</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.196399442098951</v>
+        <v>2.639768901891394</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4709424224504062</v>
+        <v>-0.004652927298764098</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.563781991821067</v>
+        <v>3.069050604748988</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.008917</t>
+          <t>X ≈ 0.00891</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.978759578587088</v>
+        <v>-3.984609538673837</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2710036318479041</v>
+        <v>0.2077103290713183</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.740027188258416</v>
+        <v>1.259721485648917</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.7945918080723757</v>
+        <v>-0.05864349358475351</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.08318326025560197</v>
+        <v>-1.273267082538823</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5236248017707084</v>
+        <v>-1.002981439275956</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-8.756348321565753</v>
+        <v>-9.020257576521118</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-10.70489844683389</v>
+        <v>-10.949338610689</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.284399121875225</v>
+        <v>-9.876012928908942</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-12.35654014042731</v>
+        <v>-13.21767971573964</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-10.33901907646528</v>
+        <v>-11.27180946064415</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-8.82315944262843</v>
+        <v>-9.772888569466282</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-7.02108807371966</v>
+        <v>-8.740391981526543</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-7.536093164233826</v>
+        <v>-8.807727819103498</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01016</t>
+          <t>X ≈ 0.01015</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.984492123704882</v>
+        <v>2.857532072750338</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.28311568018102</v>
+        <v>-2.311924867637281</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.06556021635013565</v>
+        <v>-0.9136269175745539</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.11071674008496</v>
+        <v>1.007557069191897</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7.889184509854623</v>
+        <v>6.789697719735194</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.020091888431622</v>
+        <v>4.373693338162361</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.198459697462518</v>
+        <v>1.62351135571955</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.566253438996803</v>
+        <v>2.94456258393415</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.670408897152981</v>
+        <v>1.117026022071194</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.490214871465369</v>
+        <v>3.874325346708453</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.03780729118678</v>
+        <v>5.980889447846593</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.402460672899856</v>
+        <v>2.447436096924385</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.817172204907592</v>
+        <v>4.759233105689795</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.20804546981298</v>
+        <v>3.206476165903318</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.0114</t>
+          <t>X ≈ 0.01139</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-6.832231035418843</v>
+        <v>-6.757189126046981</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.145413342647998</v>
+        <v>-4.070629820575668</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.612640767206543</v>
+        <v>5.465117104687778</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.398988803027294</v>
+        <v>1.336141118219544</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5648822372539613</v>
+        <v>-0.5830001525184443</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.165971237944419</v>
+        <v>1.11605204177188</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3901895206243537</v>
+        <v>-0.3545561785085951</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.07687912316247747</v>
+        <v>-0.8113253031051499</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1378612796852536</v>
+        <v>-0.8482979122419465</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4614952863038155</v>
+        <v>-0.2531107262150485</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.706069490362424</v>
+        <v>0.9853300461365251</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.537549091993071</v>
+        <v>6.729012884085826</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>11.46522432563623</v>
+        <v>10.64082898728568</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.343133888906223</v>
+        <v>6.604159563586762</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.01264</t>
+          <t>X ≈ 0.01263</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>55</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.736899710771283</v>
+        <v>3.750149652765764</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.907897876401769</v>
+        <v>3.936507380622977</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.331308309828593</v>
+        <v>5.470406972119832</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>11.0978970897806</v>
+        <v>9.212331147113758</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.741425718503059</v>
+        <v>6.965708944440919</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19.94789065722908</v>
+        <v>18.11110011847425</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16.22681666159927</v>
+        <v>14.341109885132</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>17.5779298359944</v>
+        <v>17.45083200465138</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>17.51694767947163</v>
+        <v>17.41385939551459</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>14.84884706495984</v>
+        <v>14.78401074780992</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>18.28050954306339</v>
+        <v>19.88847473931317</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>14.67852405905511</v>
+        <v>15.61979237013822</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>14.25837320574162</v>
+        <v>14.40706275351945</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>9.029563401422728</v>
+        <v>9.20156216098939</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>50</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-8.480916030534324</v>
+        <v>-8.510111824886955</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.092102123598181</v>
+        <v>-2.093288910042837</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-8.48687350835322</v>
+        <v>-8.487026898357541</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.643351635235149</v>
+        <v>1.642857142857146</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.105062082139476</v>
+        <v>1.153608001905248</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.5975638882254657</v>
+        <v>-0.5736064792758526</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6822742474916339</v>
+        <v>-0.6342625685013132</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.264945002391258</v>
+        <v>-4.165036966372583</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-8.230566850035906</v>
+        <v>-8.106870229007662</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.650717703349287</v>
+        <v>-2.502028155571459</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-6.424982053122783</v>
+        <v>-6.25298329355612</v>
       </c>
     </row>
     <row r="32">
@@ -1924,153 +1924,153 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.480916030534381</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-2.009955576709501</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.356648364764858</v>
+        <v>-6.44047619047619</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-8.894937917860581</v>
+        <v>-6.929725331428109</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.597563888225487</v>
+        <v>1.676393520724147</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.317725752508373</v>
+        <v>3.699070764831987</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.850657108721627</v>
+        <v>9.483238004448687</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.78967495219888</v>
+        <v>7.362932061978547</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.939756155868984</v>
+        <v>4.455770147830208</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.735054997608771</v>
+        <v>4.251629700294139</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2305668500358493</v>
+        <v>2.226463104325703</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.6507177033492582</v>
+        <v>1.831305177761877</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.424982053122733</v>
+        <v>-2.086316626889428</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.01635</t>
+          <t>X ≈ 0.01634</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.6440839694656901</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.15789787640184</v>
+        <v>-1.152112439454577</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.76312649164678</v>
+        <v>1.39532604281893</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.893351635235142</v>
+        <v>1.52521008403361</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-8.01993791786051</v>
+        <v>-10.72874493927125</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-10.84756388822544</v>
+        <v>-13.39713589104056</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.817725752508345</v>
+        <v>4.189266843263418</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10.47565710872166</v>
+        <v>6.664610553468307</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.289674952198808</v>
+        <v>3.686461473743257</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.439756155868992</v>
+        <v>2.862632892928318</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.48505499760884</v>
+        <v>8.540845386568648</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.14443314996408</v>
+        <v>-0.2245172878311621</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.849282296650671</v>
+        <v>2.321501256193251</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.200017946877203</v>
+        <v>5.51172258879685</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.01759</t>
+          <t>X ≈ 0.01758</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>26</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-10.17322372284202</v>
+        <v>-10.20241951719465</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-7.938255969752049</v>
+        <v>-7.939442756196705</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-27.5637965852763</v>
+        <v>-27.56394997528062</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-27.43357144168793</v>
+        <v>-27.43406593406594</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-24.12570714862978</v>
+        <v>-24.07716122886401</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-31.52064081130239</v>
+        <v>-31.49668340235278</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-39.29765886287622</v>
+        <v>-39.2496471838859</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-28.22626596820148</v>
+        <v>-28.17701840580776</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-20.59494043241654</v>
+        <v>-20.52168332263684</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-25.29101307490024</v>
+        <v>-25.19166574960567</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-21.64956038700659</v>
+        <v>-21.54965235098791</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-17.76902838849741</v>
+        <v>-17.64533176746917</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-22.03533308796467</v>
+        <v>-21.88664354018685</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-21.80959743773817</v>
+        <v>-21.63759867817151</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4075</v>
+        <v>4086</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.014191601559574</v>
+        <v>0.01489427416156275</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1285976561913884</v>
+        <v>0.1282825882490144</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.05711335172082244</v>
+        <v>-0.05695611485742091</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1353956988826326</v>
+        <v>0.1350446428571388</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1246507207290719</v>
+        <v>0.1230829713801924</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1415984923770353</v>
+        <v>0.1406094464691421</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1682892017979327</v>
+        <v>0.1666169819506749</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1067217987485805</v>
+        <v>0.1051832634907086</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.08379259925767713</v>
+        <v>0.08170497813596711</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.05645142431713879</v>
+        <v>0.05377340781392803</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.06168569893297615</v>
+        <v>0.05897868537606854</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.06082387844094228</v>
+        <v>0.05751333263620495</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.07155903855454682</v>
+        <v>0.06758280601405886</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.007804139012328903</v>
+        <v>-0.01216097343861122</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4054</v>
+        <v>4065</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.05898340206127273</v>
+        <v>-0.05792938251327939</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.06431696149773813</v>
+        <v>0.06417981696231578</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.002671387095730893</v>
+        <v>0.002668881819097635</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1216980919280601</v>
+        <v>0.1213847502191001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2367381835423501</v>
+        <v>0.2346094746592726</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.2030269537243186</v>
+        <v>0.2017433856885447</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2056843833874638</v>
+        <v>0.2036549167639166</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.09696252744083722</v>
+        <v>0.09518838519050377</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.07422779772731047</v>
+        <v>0.07177727082375895</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.05114107454814132</v>
+        <v>0.04795086381285785</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.03281196088215665</v>
+        <v>0.02965329911420156</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.03176056613769873</v>
+        <v>0.02787282484041498</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.04472002784676476</v>
+        <v>0.04002791919489823</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.01310378802179457</v>
+        <v>0.007779314069985332</v>
       </c>
     </row>
     <row r="8">
@@ -2318,153 +2318,153 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4014</v>
+        <v>4025</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.03492646013455669</v>
+        <v>-0.03363832315344695</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.05593563099695587</v>
+        <v>0.05583172409142634</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2011592226389354</v>
+        <v>-0.2006046981593244</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.09166177440015133</v>
+        <v>0.09143211187820555</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.06404791360849771</v>
+        <v>0.06188762510799251</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1264540133160565</v>
+        <v>0.1251289534045341</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1299615147565589</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02496478182563777</v>
+        <v>-0.0269124958407474</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1717582401375495</v>
+        <v>-0.1742887816939103</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.08712288843165794</v>
+        <v>-0.09095360496201721</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.103630588649601</v>
+        <v>-0.1074401441282333</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.08016844366137832</v>
+        <v>-0.08501773335329688</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.03801533722226225</v>
+        <v>-0.04400530410598691</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.0722167317475666</v>
+        <v>-0.07907025007782664</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01402</t>
+          <t>X &gt; -0.01401</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3964</v>
+        <v>3975</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.04611439440906651</v>
+        <v>0.04756119417018567</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1835517999430607</v>
+        <v>0.1831093844141449</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.09693640143498072</v>
+        <v>-0.09666061637058476</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.07213875149080451</v>
+        <v>0.07196630220469302</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.0006070104052398051</v>
+        <v>-0.002014488054612684</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.03486310069698817</v>
+        <v>0.03347361110827762</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.03608940740097211</v>
+        <v>-0.03858200596992134</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2375041003463849</v>
+        <v>-0.2395075368725941</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.3602368643796297</v>
+        <v>-0.3631985912877767</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2134696505826241</v>
+        <v>-0.2182476120759418</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1772212816954664</v>
+        <v>-0.1821309834665428</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2043439554317388</v>
+        <v>-0.2104659041396459</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1563923565649148</v>
+        <v>-0.1639999865573714</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.09299416210357947</v>
+        <v>-0.102039897329675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01278</t>
+          <t>X &gt; -0.01277</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3906</v>
+        <v>3917</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1090303843674008</v>
+        <v>0.1107533150621265</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3744624501639393</v>
+        <v>0.3734965315453564</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.01912598105193553</v>
+        <v>0.01908308127585912</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2398787036723249</v>
+        <v>0.2392411510058494</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1242191702620516</v>
+        <v>0.1204954191237633</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.07795987263299509</v>
+        <v>0.07607504938656717</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.01833353703928964</v>
+        <v>-0.02162240540243232</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2158050589675327</v>
+        <v>-0.2186270648010478</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.3650169424572454</v>
+        <v>-0.3690924153289501</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2546172456655356</v>
+        <v>-0.2608200077423248</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2148043014446657</v>
+        <v>-0.221159415352119</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1916722748055832</v>
+        <v>-0.1997510659558301</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.111173295875524</v>
+        <v>-0.1212216216255655</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.05017406541153946</v>
+        <v>-0.06202082227705574</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3817</v>
+        <v>3828</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.05271759711398261</v>
+        <v>-0.04981502717805597</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3085246719097867</v>
+        <v>0.3077527566238345</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.0847043390866915</v>
+        <v>0.08447609721422111</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2814493619139995</v>
+        <v>0.280689347130199</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.04494707952574828</v>
+        <v>0.04023818173320848</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.03547238495749383</v>
+        <v>-0.03763150534467741</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1320650424707139</v>
+        <v>-0.136218239948505</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.3232900531931051</v>
+        <v>-0.3270123867876293</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5269132215321832</v>
+        <v>-0.5323196990441446</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4988724753793718</v>
+        <v>-0.5068255376255806</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.374892646370256</v>
+        <v>-0.3832567523291956</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3258797591743985</v>
+        <v>-0.3366352420624636</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2599371899915113</v>
+        <v>-0.2732477951640462</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1504208794261288</v>
+        <v>-0.1662539309646576</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3707</v>
+        <v>3718</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.0615611918246799</v>
+        <v>-0.0576862017296591</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.008462544323300847</v>
+        <v>0.008587765560385208</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2372769510643593</v>
+        <v>-0.2365576036404562</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1731670626394859</v>
+        <v>-0.1725935009196817</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3470369490769158</v>
+        <v>-0.352160712878792</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4656661762470051</v>
+        <v>-0.4673262860391389</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.5627265899795191</v>
+        <v>-0.5671484745415825</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.6920307447661216</v>
+        <v>-0.6962285190028084</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.9269198753873553</v>
+        <v>-0.933468690103112</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.8729627878119572</v>
+        <v>-0.8829814194275087</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.7932468891836564</v>
+        <v>-0.8035749937845154</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7169513202434885</v>
+        <v>-0.7305261429861289</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.5557878220116379</v>
+        <v>-0.5730149799866311</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.5846799220194399</v>
+        <v>-0.6047853376658239</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3619</v>
+        <v>3630</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.113074620842724</v>
+        <v>-0.1082452314200566</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2226446738598113</v>
+        <v>-0.2217897337660659</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4097385221273271</v>
+        <v>-0.408477049414941</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4575025945802409</v>
+        <v>-0.4560439560439633</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7053017546852516</v>
+        <v>-0.7106404179903478</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.806552032697482</v>
+        <v>-0.8078010917002558</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.8488489854949393</v>
+        <v>-0.8536741714708</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8872739257611286</v>
+        <v>-0.8921745368054417</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.098846019103576</v>
+        <v>-1.10680659001595</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.105786212334159</v>
+        <v>-1.117748472606387</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.01922440603559</v>
+        <v>-1.031538480272886</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.052439260972079</v>
+        <v>-1.06832397350103</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.8772370403658627</v>
+        <v>-0.8975114934948962</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.8847775767480641</v>
+        <v>-0.9086306764762</v>
       </c>
     </row>
     <row r="14">
@@ -2630,881 +2630,881 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3485</v>
+        <v>3496</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3654214622095893</v>
+        <v>-0.3585016795464284</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.30314015619755</v>
+        <v>-0.3019548165422705</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.5681092062937267</v>
+        <v>-0.5662969297233786</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5655181787848846</v>
+        <v>-0.5636459946214671</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6877255538078941</v>
+        <v>-0.6951794445997734</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.9474064304527801</v>
+        <v>-0.9491772555315592</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.131300593425195</v>
+        <v>-1.137259999274931</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.067417941407278</v>
+        <v>-1.073824626428923</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.399436795652157</v>
+        <v>-1.409561511286235</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.402748859894842</v>
+        <v>-1.418039375979298</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.33375234184075</v>
+        <v>-1.349375348767495</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.484366677968197</v>
+        <v>-1.504240154679451</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.315089476154796</v>
+        <v>-1.340461098093627</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.475197261157192</v>
+        <v>-1.504699540695675</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.006578</t>
+          <t>X &gt; -0.006579</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3337</v>
+        <v>3348</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.421214537997038</v>
+        <v>-0.4125218219116817</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3745745034130437</v>
+        <v>-0.373050814804742</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7831698046495106</v>
+        <v>-0.7805666423289637</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7265318425061196</v>
+        <v>-0.7240279077682317</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.9200425203710125</v>
+        <v>-0.9292040326494444</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.144649090019193</v>
+        <v>-1.146908028739503</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.392800563281099</v>
+        <v>-1.40028343288283</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.574709328610112</v>
+        <v>-1.581908089767182</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.769271786281102</v>
+        <v>-1.781863643359955</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.854916097947232</v>
+        <v>-1.873784346998733</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.77392703831935</v>
+        <v>-1.793207661687354</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.022720189359028</v>
+        <v>-2.047168736470319</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.73759607363089</v>
+        <v>-1.769272108990393</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.944910132235734</v>
+        <v>-1.981776602994564</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.005338</t>
+          <t>X &gt; -0.00534</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3167</v>
+        <v>3178</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3111047097796273</v>
+        <v>-0.3007730596096394</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1443198021134435</v>
+        <v>-0.1434456498547476</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.6794474542311306</v>
+        <v>-0.67705512037071</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5952382294170491</v>
+        <v>-0.593027424269593</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.8332250715129419</v>
+        <v>-0.8457644486752613</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.085752864603421</v>
+        <v>-1.089614012232538</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.248121758518728</v>
+        <v>-1.259066336162221</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.477738731177524</v>
+        <v>-1.488286283658525</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.83705896961704</v>
+        <v>-1.854001648357617</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.913287048167589</v>
+        <v>-1.938269240395208</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.943178440877006</v>
+        <v>-1.968243505196796</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.080992851929217</v>
+        <v>-2.113159537183726</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.600212652844235</v>
+        <v>-1.642009281711751</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.830728816621331</v>
+        <v>-1.879163280969557</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.004099</t>
+          <t>X &gt; -0.004101</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2975</v>
+        <v>2986</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2720806891688881</v>
+        <v>-0.25936157480362</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.343786728092482</v>
+        <v>0.3430019505308763</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3676504674958849</v>
+        <v>-0.3662394442367543</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.08221260675942688</v>
+        <v>0.08210947930573553</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4043212958766418</v>
+        <v>-0.4223519313168111</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.55800639576821</v>
+        <v>-0.5655904472117186</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6916639188531377</v>
+        <v>-0.7084356389991413</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8387088758473169</v>
+        <v>-0.8554429224675388</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.149922363237394</v>
+        <v>-1.175182281050546</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.310327764909793</v>
+        <v>-1.345511903451822</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.4294849620957</v>
+        <v>-1.464468214281517</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.645414011607926</v>
+        <v>-1.689199546276711</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.072760714101975</v>
+        <v>-1.128743923900885</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.500612305223591</v>
+        <v>-1.564436742986764</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.002859</t>
+          <t>X &gt; -0.002862</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2753</v>
+        <v>2764</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4201785034193861</v>
+        <v>-0.4035219797303355</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2659448926766856</v>
+        <v>0.2655007153173869</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1815189497425109</v>
+        <v>-0.1807205920512374</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1764094939722369</v>
+        <v>-0.175455762694412</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5140545000473793</v>
+        <v>-0.5369798091297611</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7764845691381836</v>
+        <v>-0.7857276913970708</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7692307692307665</v>
+        <v>-0.7908847265670005</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.8543084585128753</v>
+        <v>-0.8762686140832088</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.113153184131825</v>
+        <v>-1.146457609382956</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.435651896361691</v>
+        <v>-1.481127732709268</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.620532810809195</v>
+        <v>-1.665579069733568</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.602617666732797</v>
+        <v>-1.66001556523323</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.167783789042822</v>
+        <v>-1.239822007289355</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.430430654648362</v>
+        <v>-1.513475334077079</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.00162</t>
+          <t>X &gt; -0.001623</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2477</v>
+        <v>2488</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1114381188877616</v>
+        <v>-0.09107943784179895</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1346895080899415</v>
+        <v>-0.1332889100428432</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4273879778065961</v>
+        <v>-0.4254022484975977</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.556889619288377</v>
+        <v>-0.5541004231957061</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.7115107255838069</v>
+        <v>-0.7414660870014629</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.7947469868170174</v>
+        <v>-0.8075808382502174</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.8980552458813307</v>
+        <v>-0.9268477388419996</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9004504224906142</v>
+        <v>-0.9300873096384592</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.221606272619837</v>
+        <v>-1.266229590648813</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.646700917891586</v>
+        <v>-1.707284961854093</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.071396615294418</v>
+        <v>-2.130512678937762</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.853802025509864</v>
+        <v>-1.930163401698394</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.485261690435649</v>
+        <v>-1.580372872325178</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.600597717232567</v>
+        <v>-1.711182650469276</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003802</t>
+          <t>X &gt; -0.0003839</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2220</v>
+        <v>2231</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4432984756754124</v>
+        <v>-0.4369954628718276</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.05984405908205304</v>
+        <v>-0.05851405493806539</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3407506934720033</v>
+        <v>-0.3389448287768175</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.5449891719397471</v>
+        <v>-0.5418818129661531</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7899581062858587</v>
+        <v>-0.8285348552376419</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4682999744014111</v>
+        <v>-0.4869606552472661</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.2022562861086</v>
+        <v>-1.238373381727406</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.9714453171543838</v>
+        <v>-1.009795820614656</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.142909317464074</v>
+        <v>-1.201468653584953</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.563840966433162</v>
+        <v>-1.643223140760377</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.654058812557636</v>
+        <v>-1.733523985172887</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.550098803231201</v>
+        <v>-1.650981290360079</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.180208923520375</v>
+        <v>-1.304895539084008</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.334891963032661</v>
+        <v>-1.479339187773931</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0008593</t>
+          <t>X &gt; 0.0008552</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1953</v>
+        <v>1963</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.3424231588439284</v>
+        <v>-0.4067159809944343</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.5181882482815965</v>
+        <v>0.493634556758991</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1512508545417788</v>
+        <v>0.1505808056465128</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.0476223576256416</v>
+        <v>-0.02364057635219297</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7112644484728037</v>
+        <v>-0.7388869271008716</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1820457667349089</v>
+        <v>-0.1849712687228333</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.209342684672428</v>
+        <v>-1.233247340074918</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.138101194804172</v>
+        <v>-1.164087202932393</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.8924916293034499</v>
+        <v>-0.9195882632247105</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.486917323947054</v>
+        <v>-1.512497942323975</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.30584479789222</v>
+        <v>-1.332890476036816</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9364492029770517</v>
+        <v>-0.992366412213741</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.8677084914762077</v>
+        <v>-0.9521299885653534</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9206297745769234</v>
+        <v>-1.031383701095571</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.002099</t>
+          <t>X &gt; 0.002094</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1689</v>
+        <v>1698</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.06915132465199747</v>
+        <v>-0.109643440812043</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7048372525054134</v>
+        <v>0.6490998487393611</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.519015773154436</v>
+        <v>0.4895538978953837</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.0254757071337508</v>
+        <v>-0.02459016393442681</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.8855039555963984</v>
+        <v>-0.9506685065892171</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.08428955194227683</v>
+        <v>-0.1187412975642417</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.43552100073839</v>
+        <v>-1.49643265647785</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6898036118926711</v>
+        <v>-0.7573723241898165</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6326522775707915</v>
+        <v>-0.7037150313861034</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.128170601366683</v>
+        <v>-1.201789585816464</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>-0.7858482538504816</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2873379913723682</v>
+        <v>-0.4009878760664591</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2010135613374473</v>
+        <v>-0.3513512868251425</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1173506881442634</v>
+        <v>-0.06923771051722127</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.003338</t>
+          <t>X &gt; 0.003333</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.03769510830448297</v>
+        <v>-0.08026925130724294</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.486410273096034</v>
+        <v>1.416635799060515</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3718446170775209</v>
+        <v>0.338435113962781</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1261102559247931</v>
+        <v>0.1260878067859537</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5816183871497174</v>
+        <v>-0.6683098063139639</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.8582372167469146</v>
+        <v>0.8067910532806906</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.984969479005116</v>
+        <v>-1.067733076045897</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5850275385812793</v>
+        <v>-0.6731907303946087</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.7151659883267385</v>
+        <v>-0.8101448610983795</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.565084784656598</v>
+        <v>-1.665363872788326</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.8015978377992212</v>
+        <v>-0.8693010654096653</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.07565675321706777</v>
+        <v>-0.1536699537151307</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.01171355397169549</v>
+        <v>-0.0970694778855119</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.02359797007777331</v>
+        <v>-0.1537413914196364</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.004578</t>
+          <t>X &gt; 0.004572</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.1038668502064795</v>
+        <v>-0.1097863570269269</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.691326916598705</v>
+        <v>1.643082123317619</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.6034384785104976</v>
+        <v>0.5984084149052791</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4502538538053926</v>
+        <v>0.4841915610833354</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2896747599658198</v>
+        <v>-0.367564636531263</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>0.9276160146116723</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.469753654410908</v>
+        <v>-1.53475196491241</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.15099169589503</v>
+        <v>-1.222544308476493</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.9646531599198624</v>
+        <v>-1.052100617760019</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.48481103291914</v>
+        <v>-1.586407557266526</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.8651098828528703</v>
+        <v>-0.9277210907587801</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1712098838363758</v>
+        <v>-0.2510143731517829</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.06816110951138654</v>
+        <v>-0.02661831950588578</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.04657606723998953</v>
+        <v>-0.05938198100482595</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.005818</t>
+          <t>X &gt; 0.005812</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5493869997686787</v>
+        <v>0.5429412281660717</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.620739130193527</v>
+        <v>1.56236674561282</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.03343221280666597</v>
+        <v>-0.1326725440031922</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5572562675004136</v>
+        <v>-0.6033891033891052</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.345242177495443</v>
+        <v>-1.439578370840266</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1813202334031274</v>
+        <v>-0.164788844005308</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.938371808467238</v>
+        <v>-1.92885174685803</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.694058338432846</v>
+        <v>-1.740015088162494</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.856666511215778</v>
+        <v>-1.924216532398965</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.096829209984662</v>
+        <v>-2.292554810293723</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.9803921568627416</v>
+        <v>-1.134855879853411</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.4378839232066056</v>
+        <v>-0.6184512964799396</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.05659936982144131</v>
+        <v>-0.1512217039585622</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.5306731100333195</v>
+        <v>-0.6525796608618393</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.007057</t>
+          <t>X &gt; 0.007051</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.541753994654556</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.645602794434602</v>
+        <v>1.476172917241271</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1848436633639494</v>
+        <v>-0.04397308108595155</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2577637717711667</v>
+        <v>0.08591096012872868</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5911404495061205</v>
+        <v>-0.9039639630509697</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.4784257386690669</v>
+        <v>-0.6311784442320416</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.763492521603311</v>
+        <v>-1.943398989026967</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.103657612090558</v>
+        <v>-2.217889815100193</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.418446875212311</v>
+        <v>-2.564922392224716</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.380040798445727</v>
+        <v>-2.568936719841467</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.9349957638125233</v>
+        <v>-1.07069734373102</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3930033982592249</v>
+        <v>-0.5653085161612879</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.3289777281227941</v>
+        <v>0.1184005960048324</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.4605150480466094</v>
+        <v>-0.571165111737912</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.008297</t>
+          <t>X &gt; 0.00829</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.8575394071577236</v>
+        <v>-0.9803211646615466</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5961671642485911</v>
+        <v>-0.7921616958721387</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4152122705682046</v>
+        <v>-0.8638384925604328</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.5230431445364729</v>
+        <v>-0.8949850471589613</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8099705975991185</v>
+        <v>-1.384234188110881</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5877439209586868</v>
+        <v>-0.950418073478744</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.0593234278195</v>
+        <v>-2.460349525023055</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.870654366688207</v>
+        <v>-2.121029306340368</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.931636523210983</v>
+        <v>-2.233842131569837</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.617620893311333</v>
+        <v>-2.972205081033529</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1284976205596138</v>
+        <v>-0.1779819501912954</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.148599636921119</v>
+        <v>-1.487745431600828</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.5623970507490696</v>
+        <v>0.1538160002726983</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.343014840007996</v>
+        <v>-1.618836952092671</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.009536</t>
+          <t>X &gt; 0.009529</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.02954422051166716</v>
+        <v>-0.1192594340345892</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.842626232612858</v>
+        <v>-1.078735895489828</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.027754011497876</v>
+        <v>-1.472473883804533</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.8975288679095144</v>
+        <v>-1.134689634689636</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.016531209265167</v>
+        <v>-1.416038567741353</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.605967249570007</v>
+        <v>-0.9353528410222083</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1559584580179418</v>
+        <v>-0.5802085144472571</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.6401307929321476</v>
+        <v>0.4092601804708522</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.1580960048304263</v>
+        <v>-0.04351284446636328</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1502824716584712</v>
+        <v>-0.03574059368051508</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.103476050240381</v>
+        <v>3.001629700294139</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.032591044700958</v>
+        <v>0.8868667229756682</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.717703349282296</v>
+        <v>2.702992764930634</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.4171232100351361</v>
+        <v>0.4415773758999677</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.01078</t>
+          <t>X &gt; 0.01077</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.8504812479256643</v>
+        <v>-1.019596919737928</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4136280091567599</v>
+        <v>-0.7057550347040831</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.353358521977199</v>
+        <v>-1.64149844307299</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.495612942421531</v>
+        <v>-1.782617111885415</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.668779879713412</v>
+        <v>-3.897882512999928</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.281487593947539</v>
+        <v>-2.541086154072595</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.8571376354697691</v>
+        <v>-1.246728693162559</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.231310104393124</v>
+        <v>-0.3575479034104063</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2922922609159002</v>
+        <v>-0.3945205125472029</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.14221105724576</v>
+        <v>-1.218349093362185</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.931776309084206</v>
+        <v>2.10054568945403</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.3268101991444468</v>
+        <v>0.4148689014271483</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.092451695557813</v>
+        <v>2.08107811145851</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4140530913741216</v>
+        <v>-0.39467266685309</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.01202</t>
+          <t>X &gt; 0.01201</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>297</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.5392181976535682</v>
+        <v>0.3326975396615097</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.4533524218563585</v>
+        <v>0.08731309664612041</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-2.971721993201704</v>
+        <v>-3.316458336484629</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.168096176212671</v>
+        <v>-2.517677974199721</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.389887412810047</v>
+        <v>-4.679167917827222</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.08241237307395</v>
+        <v>-3.403037917402941</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.146920712138098</v>
+        <v>-1.457005043417702</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2671880091234868</v>
+        <v>-0.2505970011254632</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.328170165646263</v>
+        <v>-0.2875696102622598</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.514789298676469</v>
+        <v>-1.44584635161236</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.984213246767048</v>
+        <v>2.363391127272962</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.348411967880992</v>
+        <v>-1.073313182027768</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.08506113769272616</v>
+        <v>0.06362841008510145</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.216227844368547</v>
+        <v>-2.044229084801884</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>242</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4148003280550085</v>
+        <v>-0.4439961224076399</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.7863169996312394</v>
+        <v>-0.7875037860758951</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.313319789344952</v>
+        <v>-5.313473179349273</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-5.18309464575659</v>
+        <v>-5.183589138134593</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-7.374276760835755</v>
+        <v>-7.325730841069984</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-8.316572152688273</v>
+        <v>-8.29261474373866</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-5.0954973879875</v>
+        <v>-5.047485708997179</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.322896610286641</v>
+        <v>-4.273649047892924</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.383878766809417</v>
+        <v>-4.310621657029721</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-5.233797563139277</v>
+        <v>-5.134450237844703</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.719490456936661</v>
+        <v>-1.619582420917986</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.99089742854828</v>
+        <v>-4.867200807520035</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.344932579382345</v>
+        <v>-3.196243031604517</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.77208949113929</v>
+        <v>-4.600090731572628</v>
       </c>
     </row>
     <row r="32">
@@ -3569,202 +3569,202 @@
         <v>192</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.685750636132312</v>
+        <v>1.65655484177968</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4462687902648454</v>
+        <v>-0.4474555767095012</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.96081503143153</v>
+        <v>-6.961309523809533</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-9.582437917860553</v>
+        <v>-9.533891998094781</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-10.32673055489214</v>
+        <v>-10.30277314594252</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-6.244774247491634</v>
+        <v>-6.196762568501313</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-4.107676224611708</v>
+        <v>-4.058428662217992</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-4.168658381134485</v>
+        <v>-4.095401271354788</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-5.018577177464344</v>
+        <v>-4.919229852169771</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.056611669057865</v>
+        <v>-0.95670363303919</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.147233516702542</v>
+        <v>-4.023536895674297</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.525717703349287</v>
+        <v>-3.377028155571459</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.341648719789418</v>
+        <v>-4.169649960222756</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.01573</t>
+          <t>X &gt; 0.01572</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.152886786367063</v>
+        <v>3.045443730668573</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.8374753411905544</v>
+        <v>0.07337775662382739</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-7.173549773215562</v>
+        <v>-7.13492063492064</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-9.824515382649281</v>
+        <v>-10.40194755365034</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-13.75249346569025</v>
+        <v>-14.29582870149807</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-8.90762636016769</v>
+        <v>-9.49537367961242</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-7.966244299729077</v>
+        <v>-8.572317551106877</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-7.32300110413918</v>
+        <v>-7.914845715799231</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-7.46869454835636</v>
+        <v>-8.044229852169764</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.039592889715138</v>
+        <v>-2.692814744150304</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-5.526341497923205</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.538041647011262</v>
+        <v>-5.113139266682573</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.31230599678473</v>
+        <v>-4.864094404667206</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.01697</t>
+          <t>X &gt; 0.01696</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>110</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.882720333102007</v>
+        <v>3.853524538749376</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.4533524218563585</v>
+        <v>0.4521656354117027</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-6.30505532653504</v>
+        <v>-6.305208716539362</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.811193819310311</v>
+        <v>-9.811688311688314</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.34948337240601</v>
+        <v>-10.30093745264023</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-14.59756388822547</v>
+        <v>-14.57360647927585</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-13.77318333840072</v>
+        <v>-13.7251716594104</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-13.33116107309656</v>
+        <v>-13.28191351070284</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-11.57396141143752</v>
+        <v>-11.50070430165782</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-11.51478929867646</v>
+        <v>-11.41544197338189</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-8.048748668217698</v>
+        <v>-7.925052047189453</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-7.559808612440193</v>
+        <v>-7.411119064662365</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-8.243163871304574</v>
+        <v>-8.071165111737912</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01821</t>
+          <t>X &gt; 0.0182</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>8.233369683751356</v>
+        <v>8.204173889398724</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>0.2748778635472249</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-6.085414108336742</v>
+        <v>-6.036868188570971</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.359468650130225</v>
+        <v>-9.335511241180612</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-5.872750437967824</v>
+        <v>-5.824738758977503</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-8.720771462706942</v>
+        <v>-8.671523900313225</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-8.781753619229718</v>
+        <v>-8.708496509450022</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-7.250720034607198</v>
+        <v>-7.151372709312625</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-1.503040240486435</v>
+        <v>-1.403132204467759</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-5.040090659559688</v>
+        <v>-4.916394038531443</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-3.079289131920717</v>
+        <v>-2.93059958414289</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.044029672170367</v>
+        <v>-3.872030912603705</v>
       </c>
     </row>
   </sheetData>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>-0.1291594439345971</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.901625933121991</v>
+        <v>-2.902812719566647</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.547124555241048</v>
+        <v>-5.547619047619051</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.768390510325986</v>
+        <v>-2.719142947932269</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.4484202858963826</v>
+        <v>-0.3751631761166863</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.8779121404659378</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>0.6408289872856798</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.098827470686771</v>
+        <v>3.270826230253434</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>105</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.757179207560888</v>
+        <v>2.727983413208257</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1936121621161035</v>
+        <v>0.1924253756714478</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2011592226389354</v>
+        <v>-0.2013126126432567</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.880457888574384</v>
+        <v>-3.880952380952387</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.228271251193888</v>
+        <v>-8.179725331428116</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-6.026135316796896</v>
+        <v>-6.002177907847283</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.158464723682108</v>
+        <v>-5.110453044691788</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.816009557945037</v>
+        <v>-1.76676199555132</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.02777019029409189</v>
+        <v>0.1010273000737882</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.830293092846901</v>
+        <v>1.930201128865576</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.864671245202224</v>
+        <v>1.988367866230469</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.444520391888815</v>
+        <v>1.593209939666643</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.670256042115348</v>
+        <v>1.84225480168201</v>
       </c>
     </row>
     <row r="8">
@@ -4015,150 +4015,150 @@
         <v>145</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.312187417741505</v>
+        <v>1.282991623388874</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.3906564970914701</v>
+        <v>0.3894697106468143</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.942855261316581</v>
+        <v>-1.943349753694584</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.101834469584695</v>
+        <v>-1.053288549818923</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.183770784777188</v>
+        <v>-2.159813375827575</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.57882597162957</v>
+        <v>-1.530814292639249</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.09203641906646</v>
+        <v>2.141283981460177</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>6.858640469440232</v>
+        <v>6.931897579219928</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.629411328282785</v>
+        <v>4.728758653577358</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.114365342436386</v>
+        <v>5.214273378455061</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.459088322377916</v>
+        <v>4.58278494340616</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>3.747016706443908</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01402</t>
+          <t>X &lt; -0.01401</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>195</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6860442356625498</v>
+        <v>-0.7152400300151811</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.297230328726378</v>
+        <v>-2.298417115171034</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.923382901903189</v>
+        <v>1.923229511898867</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.023315031431522</v>
+        <v>-1.023809523809526</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.4896774667548343</v>
+        <v>0.5382233865206061</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2742309835694101</v>
+        <v>0.2981883925190232</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.240802675585286</v>
+        <v>2.288814354575607</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.876298134362656</v>
+        <v>5.925545696756373</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.892239054762953</v>
+        <v>8.96549616454265</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.991038207151043</v>
+        <v>6.090385532445616</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.273516536070339</v>
+        <v>5.373424572089014</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.820715201246173</v>
+        <v>5.944411822274418</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.887743835112254</v>
+        <v>5.036433382890081</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.062197434056735</v>
+        <v>3.234196193623397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01278</t>
+          <t>X &lt; -0.01277</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>253</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.492773738044228</v>
+        <v>-1.521969532396859</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.684987499092252</v>
+        <v>-4.686174285536907</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3366758798947203</v>
+        <v>-0.3368292698990416</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.368506072274734</v>
+        <v>-3.369000564652737</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.535254123394147</v>
+        <v>-1.486708203628375</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4473662597669659</v>
+        <v>-0.4234088508173528</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.444207965947101</v>
+        <v>1.492219644937421</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.139194658128744</v>
+        <v>4.188442220522461</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.845010920578297</v>
+        <v>6.918268030357993</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.204578290256343</v>
+        <v>5.303925615550916</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.604620215000111</v>
+        <v>4.704528251018786</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.243741450359373</v>
+        <v>4.367438071387618</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.033076763053877</v>
+        <v>3.181766310831705</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.677784745296215</v>
+        <v>1.849783504862877</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>342</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.7354582384715016</v>
+        <v>0.7062624441188703</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.630113819504615</v>
+        <v>-2.631300605949271</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9781015785286584</v>
+        <v>-0.9782549685329798</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.894660060671292</v>
+        <v>-2.895154553049295</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2165753447611394</v>
+        <v>-0.1680294249953675</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>0.9819490762797045</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.335269612157489</v>
+        <v>2.38328129114781</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.207382254920454</v>
+        <v>4.25662981731417</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>6.777979045766102</v>
+        <v>6.851236155545799</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>6.512855571073672</v>
+        <v>6.612202896368245</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.138563769538628</v>
+        <v>5.238471805557303</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.588146600256515</v>
+        <v>4.711843221284759</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.875598086124398</v>
+        <v>4.024287633902226</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.346947771438657</v>
+        <v>2.518946531005319</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>452</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.6164291022090183</v>
+        <v>0.5872333078563869</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5539155755168679</v>
+        <v>0.5527287890722121</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.929055695186605</v>
+        <v>1.928902305182284</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.616802962668771</v>
+        <v>1.616308470290768</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.069663852050951</v>
+        <v>3.118209771816723</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.251993633898429</v>
+        <v>4.275951042848043</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.273477964897744</v>
+        <v>5.321489643888064</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.133842949429592</v>
+        <v>6.183090511823309</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>8.285250173437795</v>
+        <v>8.358507283217492</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.877809253214132</v>
+        <v>7.977156578508705</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.230630218847743</v>
+        <v>7.330538254866418</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.601291557043766</v>
+        <v>6.72498817807201</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.296184951517965</v>
+        <v>5.444874499295793</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.300681663691407</v>
+        <v>5.472680423258069</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>540</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8524173027989832</v>
+        <v>0.8232215084463519</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.019008987512933</v>
+        <v>2.017822201068277</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.735348713869001</v>
+        <v>2.73519532386468</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.235944227827737</v>
+        <v>3.235449735449734</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.919876896954257</v>
+        <v>4.968422816720029</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.772806482144908</v>
+        <v>5.796763891094521</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.243651678434297</v>
+        <v>6.291663357424618</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>6.332138590203108</v>
+        <v>6.381386152596825</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>7.937823100347003</v>
+        <v>8.0110802101267</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>8.013830229943068</v>
+        <v>8.113177555237641</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7.438758701312508</v>
+        <v>7.538666737331184</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>7.658322038853008</v>
+        <v>7.782018659881253</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.497430444798866</v>
+        <v>6.646119992576693</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.352795724655024</v>
+        <v>6.524794484221687</v>
       </c>
     </row>
     <row r="14">
@@ -4327,878 +4327,878 @@
         <v>674</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.9701225451333</v>
+        <v>1.940926750780669</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.990983929814284</v>
+        <v>1.989797143369628</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.931524117759544</v>
+        <v>2.931370727755223</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.061749261347906</v>
+        <v>3.061254768969903</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.710403328430246</v>
+        <v>3.758949248196018</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.194720978243382</v>
+        <v>5.218678387192995</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.296954239155255</v>
+        <v>6.344965918145576</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.829885595368516</v>
+        <v>5.879133157762233</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7.697686821635045</v>
+        <v>7.770943931414742</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>7.737975740438728</v>
+        <v>7.837323065733301</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>7.384906629656285</v>
+        <v>7.484814665674961</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.161124544622872</v>
+        <v>8.284821165651117</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>7.295869833742707</v>
+        <v>7.444559381520534</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.966709341535996</v>
+        <v>8.138708101102658</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.006578</t>
+          <t>X &lt; -0.006579</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>822</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.776991512044724</v>
+        <v>1.747795717692092</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.868968436012523</v>
+        <v>1.867781649567867</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.177360068289111</v>
+        <v>3.17720667828479</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.064276209444387</v>
+        <v>3.063781717066384</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.864186169730687</v>
+        <v>3.912732089496458</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.891487206665047</v>
+        <v>4.915444615614661</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6.023321859564327</v>
+        <v>6.071333538554647</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.651143726726495</v>
+        <v>6.700391289120212</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7.56339757993608</v>
+        <v>7.636654689715776</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.930023795771667</v>
+        <v>8.029371121066241</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.603668136294935</v>
+        <v>7.70357617231361</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>8.611282298382612</v>
+        <v>8.734978919410857</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.461204437769936</v>
+        <v>7.609893985547764</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>8.173558092862656</v>
+        <v>8.345556852429318</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.005338</t>
+          <t>X &lt; -0.00534</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>992</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.047309775917263</v>
+        <v>1.018113981564632</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7466075538211712</v>
+        <v>0.7454207673765154</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.166352298098396</v>
+        <v>2.166198908094074</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.994158086848039</v>
+        <v>1.993663594470036</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.766352404720095</v>
+        <v>2.814898324485867</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.668565144032598</v>
+        <v>3.692522552982211</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.28949994605675</v>
+        <v>4.337511625047071</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.931302270011955</v>
+        <v>4.980549832405671</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>6.180803984456915</v>
+        <v>6.254061094236611</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.439756155868992</v>
+        <v>6.539103481163565</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>6.537474352447511</v>
+        <v>6.637382388466186</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.97507831125445</v>
+        <v>7.098774932282694</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.446056490199098</v>
+        <v>5.594746037976925</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6.075017946877246</v>
+        <v>6.247016706443908</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.004099</t>
+          <t>X &lt; -0.004101</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1184</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7285434289251072</v>
+        <v>0.6993476345724758</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.6292642857603425</v>
+        <v>-0.6304510722049983</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9185318970521834</v>
+        <v>0.9183785070478621</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1336753917918898</v>
+        <v>-0.1341698841698928</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.101683703761069</v>
+        <v>1.15022962352684</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.567976652315075</v>
+        <v>1.591934061264688</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.990023049805671</v>
+        <v>2.038034728795992</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.283089541154062</v>
+        <v>2.332337103547779</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.151161438685342</v>
+        <v>3.224418548465039</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.56813453424737</v>
+        <v>3.667481859541944</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.870190132743929</v>
+        <v>3.970098168762604</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.411325041856017</v>
+        <v>4.535021662884262</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.977660675029092</v>
+        <v>3.12635022280692</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3.963531460390755</v>
+        <v>4.135530219957417</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.002859</t>
+          <t>X &lt; -0.002862</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1406</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8619004701768773</v>
+        <v>0.832704675824246</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.3225430908812541</v>
+        <v>-0.3237298773259099</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3495418543779323</v>
+        <v>0.3493884643736109</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.4086432426320101</v>
+        <v>0.4081487502540071</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.079457530219109</v>
+        <v>1.128003449984881</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.661326581191325</v>
+        <v>1.685283990140938</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.718863732593711</v>
+        <v>1.766875411584031</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.82078513148123</v>
+        <v>1.870032693874947</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.399916772966989</v>
+        <v>2.473173882746686</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.043596838657045</v>
+        <v>3.142944163951618</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.407885723071097</v>
+        <v>3.507793759089772</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.371140120092143</v>
+        <v>3.494836741120388</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.524246734773051</v>
+        <v>2.672936282550879</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.963353651002421</v>
+        <v>3.135352410569084</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.00162</t>
+          <t>X &lt; -0.001623</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1682</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.194470414174333</v>
+        <v>0.1652746198217017</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3668752842496161</v>
+        <v>0.3656884978049604</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6260872526455898</v>
+        <v>0.6259338626412685</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8752184604432287</v>
+        <v>0.8747239680652257</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.109818324707824</v>
+        <v>1.158364244473596</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.288286290133634</v>
+        <v>1.312243699083247</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.500841091390647</v>
+        <v>1.548852770380968</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.449943672336374</v>
+        <v>1.499191234730091</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.983491836859969</v>
+        <v>2.056748946639665</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.619898843146039</v>
+        <v>2.719246168440613</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.247540134350778</v>
+        <v>3.347448170369454</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.925200094078271</v>
+        <v>3.048896715106515</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.386143176555585</v>
+        <v>2.534832724333413</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.492972762572855</v>
+        <v>2.664971522139517</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003802</t>
+          <t>X &lt; -0.0003839</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1939</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5361030514666751</v>
+        <v>0.5311252885150779</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2142413524203874</v>
+        <v>0.2130545659757317</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3867727010330668</v>
+        <v>0.3866193110287455</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6717167719035331</v>
+        <v>0.67122227952553</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9585948309790524</v>
+        <v>1.007140750744824</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6370931514857219</v>
+        <v>0.6610505604353349</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.532269331672886</v>
+        <v>1.580281010663207</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.219919615168251</v>
+        <v>1.269167177561968</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.468375313209677</v>
+        <v>1.541632422989373</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.959353886658057</v>
+        <v>2.058701211952631</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.064090582962073</v>
+        <v>2.163998618980749</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.943749808035292</v>
+        <v>2.067446429063537</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.523598954721884</v>
+        <v>1.672288502499711</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.646188653427011</v>
+        <v>1.818187412993673</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0008593</t>
+          <t>X &lt; 0.0008552</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.3270549839583978</v>
+        <v>0.3858157769229749</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.3330441525836889</v>
+        <v>-0.3132979639133637</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1390474213967039</v>
+        <v>-0.1392008114010252</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.0817574323365946</v>
+        <v>0.06061881027897442</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.675714256052494</v>
+        <v>0.7041290712300921</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2484506045281591</v>
+        <v>0.2519485728310826</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.205406911928655</v>
+        <v>1.233431133356412</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.100657108721627</v>
+        <v>1.130081381582038</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.9292309105133114</v>
+        <v>0.957177644216884</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.464688159495466</v>
+        <v>1.492660345685536</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.305317916919762</v>
+        <v>1.333830274225569</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.9770487437991164</v>
+        <v>1.029514002981493</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9195452159616764</v>
+        <v>0.996839085026636</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9186262877657327</v>
+        <v>1.019332066661391</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.002099</t>
+          <t>X &lt; 0.002094</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.06762765878603716</v>
+        <v>0.09594878117361816</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3704192757017495</v>
+        <v>-0.3341943263726606</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3606599161202126</v>
+        <v>-0.3422634531493003</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.05273674850374732</v>
+        <v>0.05224225612574429</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.6471332795504523</v>
+        <v>0.6956791993162241</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1354458205124018</v>
+        <v>0.1594032294620149</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.102515396521312</v>
+        <v>1.150527075511633</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.5545406038672596</v>
+        <v>0.6037881662609763</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5565709457237418</v>
+        <v>0.6072686315578366</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.9033189089054261</v>
+        <v>0.9565792093189103</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.617646090726204</v>
+        <v>0.6715326129154988</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3281376034054233</v>
+        <v>0.4060747548111365</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2723592197276332</v>
+        <v>0.3749944981502296</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.01226491043999545</v>
+        <v>0.1386024669617143</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.003338</t>
+          <t>X &lt; 0.003333</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2714</v>
+        <v>2719</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.03839253879260696</v>
+        <v>0.06152667621515207</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6901160993245554</v>
+        <v>-0.6570522323508072</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.202210029132921</v>
+        <v>-0.1855563101222515</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.03520665825511315</v>
+        <v>-0.03570115063311619</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3459594708853047</v>
+        <v>0.3945053906510765</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3864568635840513</v>
+        <v>-0.3624994546344382</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.6321795958331151</v>
+        <v>0.6801912748234358</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3857803157830446</v>
+        <v>0.4350278781767614</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.492397542338658</v>
+        <v>0.5451681781977413</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.9511657988575806</v>
+        <v>1.008577552513323</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.546542479199374</v>
+        <v>0.5837677412405711</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1598567227081418</v>
+        <v>0.200595751132127</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1289433135998692</v>
+        <v>0.173220097462746</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.09675707731202721</v>
+        <v>0.1648173684519989</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.004578</t>
+          <t>X &lt; 0.004572</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2946</v>
+        <v>2951</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.0597343759697111</v>
+        <v>0.06267084268241518</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6029422319992648</v>
+        <v>-0.5883786492910588</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.252456164179776</v>
+        <v>-0.2526095541840974</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1561063593448111</v>
+        <v>-0.1721208307111439</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1524875563941848</v>
+        <v>0.185800479031613</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3292712052986317</v>
+        <v>-0.3208108167885584</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.7039046142969809</v>
+        <v>0.7367980889029582</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5417140192907297</v>
+        <v>0.5759466907697046</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4996037898809931</v>
+        <v>0.5389740816329081</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7194171728181473</v>
+        <v>0.7656368596793186</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4661502841466145</v>
+        <v>0.4937227760876581</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1805593372097078</v>
+        <v>0.2130213331746802</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.08494568314544892</v>
+        <v>0.1228447688609435</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.05838522454187967</v>
+        <v>0.1007950866540028</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.005818</t>
+          <t>X &lt; 0.005812</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3175</v>
+        <v>3179</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1553346351855112</v>
+        <v>-0.1545841866960274</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4151693768979925</v>
+        <v>-0.4018028905643547</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.007155404280339894</v>
+        <v>0.03842878988884024</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.2002340990943523</v>
+        <v>0.2168904657115789</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4476139363192004</v>
+        <v>0.4821210481171008</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.1164524536978533</v>
+        <v>0.11192811191912</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.691704382300955</v>
+        <v>0.6976027979661339</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5878466717521249</v>
+        <v>0.6092472316689737</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6701780968529434</v>
+        <v>0.6981003538942403</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.7500738658406831</v>
+        <v>0.8179647582947425</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4059171750789048</v>
+        <v>0.4565421465560604</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2377995333446776</v>
+        <v>0.2945138540373478</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.0873175611343342</v>
+        <v>0.1510073901976554</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2364352697118974</v>
+        <v>0.2742265208509522</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.007057</t>
+          <t>X &lt; 0.007051</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3371</v>
+        <v>3378</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1126507848268261</v>
+        <v>-0.08694397618722149</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3028777304661503</v>
+        <v>-0.2653255639003547</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.04637617265161964</v>
+        <v>0.007355124114369005</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.03456429134863725</v>
+        <v>0.005471753918961042</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1672290448392673</v>
+        <v>0.2423653983549272</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.168569918760916</v>
+        <v>0.2059140889395934</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.4983059774935654</v>
+        <v>0.5463176564838861</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.5509828416206517</v>
+        <v>0.5837412608133903</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6546038621514541</v>
+        <v>0.6947852295333163</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.6508672669801001</v>
+        <v>0.699849484715962</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.3147823242240904</v>
+        <v>0.3476924593231487</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1880515905214892</v>
+        <v>0.2282393032599828</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.02188016141939642</v>
+        <v>0.06990790126690882</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.1754332539077978</v>
+        <v>0.2005395009968964</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.008297</t>
+          <t>X &lt; 0.00829</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3549</v>
+        <v>3555</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1625035420190741</v>
+        <v>0.1850032789872387</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1823635681903539</v>
+        <v>0.2172980037454266</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.06880703157928281</v>
+        <v>0.1478045623166224</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1146677207244622</v>
+        <v>0.1806486573274952</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1669293487311236</v>
+        <v>0.2688412790271997</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1549670454078296</v>
+        <v>0.2197587161135246</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.4358359887288401</v>
+        <v>0.5119691525335526</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.3780832690591822</v>
+        <v>0.427330831452899</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.417136966830256</v>
+        <v>0.4747464079701089</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5398124463277583</v>
+        <v>0.6073172645672216</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.06951445706825865</v>
+        <v>0.1218828648511021</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2887234907132097</v>
+        <v>0.3488259735240149</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.002830379405629913</v>
+        <v>0.06618562783219772</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.295220820926275</v>
+        <v>0.3433598850655599</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.009536</t>
+          <t>X &lt; 0.009529</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3684</v>
+        <v>3692</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.009609145426672683</v>
+        <v>0.02905619240096513</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1851041568566103</v>
+        <v>0.2163571315675341</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1299691669784906</v>
+        <v>0.1886487773181287</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1395596525699219</v>
+        <v>0.171108021472989</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1578932931933608</v>
+        <v>0.210395454582347</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1301521778812784</v>
+        <v>0.1734857576730278</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.09962767610630863</v>
+        <v>0.1546984704597207</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.02739167176617485</v>
+        <v>0.001393169085574186</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.06210650546531582</v>
+        <v>0.08762074633155237</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0677388022898171</v>
+        <v>0.09109373299133949</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3115953956648667</v>
+        <v>-0.3025945076668606</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.04499983972660004</v>
+        <v>-0.02780172101955003</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.259944297650506</v>
+        <v>-0.2604901106215607</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.008242702577575756</v>
+        <v>0.00378810406037644</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.01078</t>
+          <t>X &lt; 0.01077</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3793</v>
+        <v>3803</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.09531951100086644</v>
+        <v>0.1118074200002752</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1139967197246321</v>
+        <v>0.1422211869936163</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.1279042986412549</v>
+        <v>0.1562050009079314</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1672864064082091</v>
+        <v>0.1954680061476139</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.3799897327577</v>
+        <v>0.4029518339262239</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2708571644061095</v>
+        <v>0.2964381518609329</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1598310156662563</v>
+        <v>0.1976702046079382</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.07571633483376417</v>
+        <v>0.0877165965159179</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.108263683109854</v>
+        <v>0.1177928081687725</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1946942649024379</v>
+        <v>0.2020469765643469</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.100561440747363</v>
+        <v>-0.1187698790959786</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.05401813020127122</v>
+        <v>0.0445493293519803</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.1140809084099104</v>
+        <v>-0.1140155372749234</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1001959062761415</v>
+        <v>0.09726650923118285</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.01202</t>
+          <t>X &lt; 0.01201</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3862</v>
+        <v>3873</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.028670289698006</v>
+        <v>-0.01268649018049217</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.03799596623145618</v>
+        <v>0.06586638225692809</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2252359675052844</v>
+        <v>0.2527979342029951</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.1888061806896815</v>
+        <v>0.2164206574152345</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3621016068100715</v>
+        <v>0.3855667647918182</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2861570420070976</v>
+        <v>0.3116732319899356</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1639392443667305</v>
+        <v>0.1878106651242675</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.07299423385089199</v>
+        <v>0.07142904563172436</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1038720041771271</v>
+        <v>0.1002901631137405</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1994561041359333</v>
+        <v>0.1939421908409855</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.06830852114929087</v>
+        <v>-0.09895539693525279</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1876526116618464</v>
+        <v>0.1657162449211214</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.09274592595436104</v>
+        <v>0.08031567509452486</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2296010644329129</v>
+        <v>0.2148710828962734</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3917</v>
+        <v>3928</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.0381679389313021</v>
+        <v>0.04000235933021656</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1201656290106285</v>
+        <v>0.1199090595003085</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3247354529502431</v>
+        <v>0.323838803597269</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3415945687721944</v>
+        <v>0.3406732931872511</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.479488979745156</v>
+        <v>0.4749186445264968</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.561671780564339</v>
+        <v>0.5585073418623523</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.3890815119375191</v>
+        <v>0.3847971519561142</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.3184113784131881</v>
+        <v>0.3142412242419326</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.3480635294553522</v>
+        <v>0.342209966885747</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.4049436080495568</v>
+        <v>0.39719096844739</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1891366302618636</v>
+        <v>0.1819485335002753</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.391020289540549</v>
+        <v>0.3816793893129855</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2915998055838429</v>
+        <v>0.2808682557291249</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.3531644875971907</v>
+        <v>0.3407030608227188</v>
       </c>
     </row>
     <row r="32">
@@ -5260,205 +5260,205 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3967</v>
+        <v>3978</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.06885572902681503</v>
+        <v>-0.06711508221597029</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.0923663358137361</v>
+        <v>0.09217474910503398</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2139811925014854</v>
+        <v>0.2133992736153871</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3579606369952586</v>
+        <v>0.3569995701389814</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.487355844714898</v>
+        <v>0.4834299231492594</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.5470901998248507</v>
+        <v>0.5443062151546485</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.3756019477776178</v>
+        <v>0.372010957220148</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.2495999730558793</v>
+        <v>0.2462902132840199</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2780938847265446</v>
+        <v>0.2734266640372951</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3235385784325828</v>
+        <v>0.3173556157692872</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.1330398842586789</v>
+        <v>0.1273518806508278</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2824087105587267</v>
+        <v>0.2750393187310607</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2545242321345853</v>
+        <v>0.2458984591558604</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2677328447849803</v>
+        <v>0.2578261584298289</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.01573</t>
+          <t>X &lt; 0.01572</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4017</v>
+        <v>4026</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.0987820354971376</v>
+        <v>-0.09614797244825724</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.04043696798781582</v>
+        <v>0.06718657286949536</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1556289742684243</v>
+        <v>0.1575111249270762</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2745907710682758</v>
+        <v>0.2761574401812226</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.3708345610266761</v>
+        <v>0.3952436896375602</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.5328708943832297</v>
+        <v>0.5577767631634174</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.3873082574785514</v>
+        <v>0.4116089911317147</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.3316414487663764</v>
+        <v>0.3562538774645532</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.3341801734817977</v>
+        <v>0.357846475275494</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.3436357878013467</v>
+        <v>0.3666469054811827</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1529654453700005</v>
+        <v>0.1764869849801656</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2760268299840263</v>
+        <v>0.2982936240211629</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2432593996870551</v>
+        <v>0.2647957828442316</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2093221539969932</v>
+        <v>0.2298781073381022</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.01697</t>
+          <t>X &lt; 0.01696</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4049</v>
+        <v>4060</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0929298168465067</v>
+        <v>-0.09174698324692088</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.05712220538483592</v>
+        <v>0.05700578543849844</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1682989054398902</v>
+        <v>0.1678490534970365</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2873526206995436</v>
+        <v>0.2865917865917851</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3046677992414644</v>
+        <v>0.3022931825392803</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.4431065579170053</v>
+        <v>0.4411427832610215</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.4459308807134974</v>
+        <v>0.443190099312794</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.4116928670446924</v>
+        <v>0.4090045235501734</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3890829443054145</v>
+        <v>0.3856872895308285</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3917670120249213</v>
+        <v>0.3875286780139575</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2503560834923206</v>
+        <v>0.2464816159558012</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.298685186498318</v>
+        <v>0.2939175602587412</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2875539015889856</v>
+        <v>0.282015183507589</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2803772948644081</v>
+        <v>0.2741103025030185</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01821</t>
+          <t>X &lt; 0.0182</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4075</v>
+        <v>4086</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1570412751527499</v>
+        <v>-0.1558790851943783</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.006258532139526096</v>
+        <v>0.006271851304163079</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.008165725680676417</v>
+        <v>-0.008139907876703489</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1109158947210673</v>
+        <v>0.1106305803571388</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1491365189660883</v>
+        <v>0.1475029958002168</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.239565673371402</v>
+        <v>0.2383134034794026</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.192786996996368</v>
+        <v>0.1910489389504306</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2292407891920973</v>
+        <v>0.2273729018093746</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2553612267086578</v>
+        <v>0.2528122868624365</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2280621132114788</v>
+        <v>0.2249225520682074</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1107293477804561</v>
+        <v>0.1078903997316587</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1834630739278182</v>
+        <v>0.1798225302878649</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.145160608721369</v>
+        <v>0.1409862804451762</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1394351247913548</v>
+        <v>0.1346819046817984</v>
       </c>
     </row>
   </sheetData>
